--- a/research/traditional_assets/database/data/iceland/iceland_machinery.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_machinery.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1002093455137177</v>
+        <v>0.1000449268226903</v>
       </c>
       <c r="C2">
-        <v>626.4987918074122</v>
+        <v>621.6636997999233</v>
       </c>
       <c r="D2">
-        <v>576.9987918074122</v>
+        <v>578.7476997999232</v>
       </c>
       <c r="E2">
-        <v>-194.4</v>
+        <v>-187.816</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.584</v>
       </c>
       <c r="G2">
         <v>49.5</v>
@@ -1451,28 +1451,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3311751999999999</v>
       </c>
       <c r="N2">
-        <v>53.14666666666666</v>
+        <v>52.81549146666666</v>
       </c>
       <c r="O2">
-        <v>10.62933333333333</v>
+        <v>10.56309829333333</v>
       </c>
       <c r="P2">
-        <v>42.51733333333333</v>
+        <v>42.25239317333333</v>
       </c>
       <c r="Q2">
-        <v>46.43733333333333</v>
+        <v>46.17239317333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1002093455137177</v>
+        <v>0.1006490169926165</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.040465584384237</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>160.4790052717313</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1000449268226903</v>
+        <v>0.09988050813166284</v>
       </c>
       <c r="C3">
-        <v>621.6636997999233</v>
+        <v>616.8392420550474</v>
       </c>
       <c r="D3">
-        <v>578.7476997999232</v>
+        <v>580.5072420550474</v>
       </c>
       <c r="E3">
-        <v>-187.816</v>
+        <v>-181.232</v>
       </c>
       <c r="F3">
-        <v>6.584</v>
+        <v>13.168</v>
       </c>
       <c r="G3">
         <v>49.5</v>
@@ -1533,28 +1533,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M3">
-        <v>0.3311751999999999</v>
+        <v>0.6623503999999999</v>
       </c>
       <c r="N3">
-        <v>52.81549146666666</v>
+        <v>52.48431626666666</v>
       </c>
       <c r="O3">
-        <v>10.56309829333333</v>
+        <v>10.49686325333333</v>
       </c>
       <c r="P3">
-        <v>42.25239317333333</v>
+        <v>41.98745301333333</v>
       </c>
       <c r="Q3">
-        <v>46.17239317333333</v>
+        <v>45.90745301333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1006490169926165</v>
+        <v>0.1010976613588396</v>
       </c>
       <c r="T3">
-        <v>1.040465584384237</v>
+        <v>1.048976202227141</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>160.4790052717313</v>
+        <v>80.23950263586565</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09988050813166284</v>
+        <v>0.09971608944063541</v>
       </c>
       <c r="C4">
-        <v>616.8392420550474</v>
+        <v>612.0255158612687</v>
       </c>
       <c r="D4">
-        <v>580.5072420550474</v>
+        <v>582.2775158612686</v>
       </c>
       <c r="E4">
-        <v>-181.232</v>
+        <v>-174.648</v>
       </c>
       <c r="F4">
-        <v>13.168</v>
+        <v>19.752</v>
       </c>
       <c r="G4">
         <v>49.5</v>
@@ -1615,28 +1615,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M4">
-        <v>0.6623503999999999</v>
+        <v>0.9935255999999999</v>
       </c>
       <c r="N4">
-        <v>52.48431626666666</v>
+        <v>52.15314106666666</v>
       </c>
       <c r="O4">
-        <v>10.49686325333333</v>
+        <v>10.43062821333333</v>
       </c>
       <c r="P4">
-        <v>41.98745301333333</v>
+        <v>41.72251285333333</v>
       </c>
       <c r="Q4">
-        <v>45.90745301333333</v>
+        <v>45.64251285333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1010976613588396</v>
+        <v>0.1015555561243664</v>
       </c>
       <c r="T4">
-        <v>1.048976202227141</v>
+        <v>1.0576622967266</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>80.23950263586565</v>
+        <v>53.49300175724377</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09971608944063541</v>
+        <v>0.09955167074960798</v>
       </c>
       <c r="C5">
-        <v>612.0255158612687</v>
+        <v>607.2226196974374</v>
       </c>
       <c r="D5">
-        <v>582.2775158612686</v>
+        <v>584.0586196974374</v>
       </c>
       <c r="E5">
-        <v>-174.648</v>
+        <v>-168.064</v>
       </c>
       <c r="F5">
-        <v>19.752</v>
+        <v>26.336</v>
       </c>
       <c r="G5">
         <v>49.5</v>
@@ -1697,28 +1697,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M5">
-        <v>0.9935255999999999</v>
+        <v>1.3247008</v>
       </c>
       <c r="N5">
-        <v>52.15314106666666</v>
+        <v>51.82196586666666</v>
       </c>
       <c r="O5">
-        <v>10.43062821333333</v>
+        <v>10.36439317333333</v>
       </c>
       <c r="P5">
-        <v>41.72251285333333</v>
+        <v>41.45757269333333</v>
       </c>
       <c r="Q5">
-        <v>45.64251285333333</v>
+        <v>45.37757269333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1015555561243664</v>
+        <v>0.102022990364175</v>
       </c>
       <c r="T5">
-        <v>1.0576622967266</v>
+        <v>1.066529351528131</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.49300175724377</v>
+        <v>40.11975131793282</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09955167074960798</v>
+        <v>0.09938725205858054</v>
       </c>
       <c r="C6">
-        <v>607.2226196974374</v>
+        <v>602.4306532510328</v>
       </c>
       <c r="D6">
-        <v>584.0586196974374</v>
+        <v>585.8506532510328</v>
       </c>
       <c r="E6">
-        <v>-168.064</v>
+        <v>-161.48</v>
       </c>
       <c r="F6">
-        <v>26.336</v>
+        <v>32.92</v>
       </c>
       <c r="G6">
         <v>49.5</v>
@@ -1779,28 +1779,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M6">
-        <v>1.3247008</v>
+        <v>1.655876</v>
       </c>
       <c r="N6">
-        <v>51.82196586666666</v>
+        <v>51.49079066666666</v>
       </c>
       <c r="O6">
-        <v>10.36439317333333</v>
+        <v>10.29815813333333</v>
       </c>
       <c r="P6">
-        <v>41.45757269333333</v>
+        <v>41.19263253333333</v>
       </c>
       <c r="Q6">
-        <v>45.37757269333333</v>
+        <v>45.11263253333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.102022990364175</v>
+        <v>0.1025002653248216</v>
       </c>
       <c r="T6">
-        <v>1.066529351528131</v>
+        <v>1.075583081167589</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.11975131793282</v>
+        <v>32.09580105434625</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09938725205858054</v>
+        <v>0.0992228333675531</v>
       </c>
       <c r="C7">
-        <v>602.4306532510328</v>
+        <v>597.6497174367601</v>
       </c>
       <c r="D7">
-        <v>585.8506532510328</v>
+        <v>587.6537174367601</v>
       </c>
       <c r="E7">
-        <v>-161.48</v>
+        <v>-154.896</v>
       </c>
       <c r="F7">
-        <v>32.92</v>
+        <v>39.504</v>
       </c>
       <c r="G7">
         <v>49.5</v>
@@ -1861,28 +1861,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M7">
-        <v>1.655876</v>
+        <v>1.9870512</v>
       </c>
       <c r="N7">
-        <v>51.49079066666666</v>
+        <v>51.15961546666666</v>
       </c>
       <c r="O7">
-        <v>10.29815813333333</v>
+        <v>10.23192309333333</v>
       </c>
       <c r="P7">
-        <v>41.19263253333333</v>
+        <v>40.92769237333333</v>
       </c>
       <c r="Q7">
-        <v>45.11263253333333</v>
+        <v>44.84769237333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1025002653248216</v>
+        <v>0.102987695071865</v>
       </c>
       <c r="T7">
-        <v>1.075583081167589</v>
+        <v>1.084829443352567</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.09580105434625</v>
+        <v>26.74650087862188</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0992228333675531</v>
+        <v>0.09905841467652568</v>
       </c>
       <c r="C8">
-        <v>597.6497174367601</v>
+        <v>592.8799144154947</v>
       </c>
       <c r="D8">
-        <v>587.6537174367601</v>
+        <v>589.4679144154946</v>
       </c>
       <c r="E8">
-        <v>-154.896</v>
+        <v>-148.312</v>
       </c>
       <c r="F8">
-        <v>39.504</v>
+        <v>46.08799999999999</v>
       </c>
       <c r="G8">
         <v>49.5</v>
@@ -1943,28 +1943,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M8">
-        <v>1.9870512</v>
+        <v>2.318226399999999</v>
       </c>
       <c r="N8">
-        <v>51.15961546666666</v>
+        <v>50.82844026666666</v>
       </c>
       <c r="O8">
-        <v>10.23192309333333</v>
+        <v>10.16568805333333</v>
       </c>
       <c r="P8">
-        <v>40.92769237333333</v>
+        <v>40.66275221333333</v>
       </c>
       <c r="Q8">
-        <v>44.84769237333333</v>
+        <v>44.58275221333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.102987695071865</v>
+        <v>0.1034856071790599</v>
       </c>
       <c r="T8">
-        <v>1.084829443352567</v>
+        <v>1.094274652036147</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.74650087862188</v>
+        <v>22.9255721816759</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09905841467652567</v>
+        <v>0.09889399598549825</v>
       </c>
       <c r="C9">
-        <v>592.8799144154948</v>
+        <v>588.1213476135786</v>
       </c>
       <c r="D9">
-        <v>589.4679144154948</v>
+        <v>591.2933476135786</v>
       </c>
       <c r="E9">
-        <v>-148.312</v>
+        <v>-141.728</v>
       </c>
       <c r="F9">
-        <v>46.088</v>
+        <v>52.672</v>
       </c>
       <c r="G9">
         <v>49.5</v>
@@ -2025,28 +2025,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M9">
-        <v>2.3182264</v>
+        <v>2.6494016</v>
       </c>
       <c r="N9">
-        <v>50.82844026666666</v>
+        <v>50.49726506666666</v>
       </c>
       <c r="O9">
-        <v>10.16568805333333</v>
+        <v>10.09945301333333</v>
       </c>
       <c r="P9">
-        <v>40.66275221333333</v>
+        <v>40.39781205333333</v>
       </c>
       <c r="Q9">
-        <v>44.58275221333333</v>
+        <v>44.31781205333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1034856071790599</v>
+        <v>0.1039943434624981</v>
       </c>
       <c r="T9">
-        <v>1.094274652036147</v>
+        <v>1.103925191343283</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.9255721816759</v>
+        <v>20.05987565896642</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09889399598549825</v>
+        <v>0.09872957729447081</v>
       </c>
       <c r="C10">
-        <v>588.1213476135786</v>
+        <v>583.3741217424741</v>
       </c>
       <c r="D10">
-        <v>591.2933476135786</v>
+        <v>593.1301217424741</v>
       </c>
       <c r="E10">
-        <v>-141.728</v>
+        <v>-135.144</v>
       </c>
       <c r="F10">
-        <v>52.672</v>
+        <v>59.25599999999999</v>
       </c>
       <c r="G10">
         <v>49.5</v>
@@ -2107,28 +2107,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M10">
-        <v>2.6494016</v>
+        <v>2.9805768</v>
       </c>
       <c r="N10">
-        <v>50.49726506666666</v>
+        <v>50.16608986666666</v>
       </c>
       <c r="O10">
-        <v>10.09945301333333</v>
+        <v>10.03321797333333</v>
       </c>
       <c r="P10">
-        <v>40.39781205333333</v>
+        <v>40.13287189333333</v>
       </c>
       <c r="Q10">
-        <v>44.31781205333333</v>
+        <v>44.05287189333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1039943434624981</v>
+        <v>0.1045142607631547</v>
       </c>
       <c r="T10">
-        <v>1.103925191343283</v>
+        <v>1.113787830415411</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.05987565896642</v>
+        <v>17.83100058574792</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09872957729447081</v>
+        <v>0.09856515860344336</v>
       </c>
       <c r="C11">
-        <v>583.3741217424741</v>
+        <v>578.6383428187863</v>
       </c>
       <c r="D11">
-        <v>593.1301217424741</v>
+        <v>594.9783428187864</v>
       </c>
       <c r="E11">
-        <v>-135.144</v>
+        <v>-128.56</v>
       </c>
       <c r="F11">
-        <v>59.25599999999999</v>
+        <v>65.83999999999999</v>
       </c>
       <c r="G11">
         <v>49.5</v>
@@ -2189,28 +2189,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M11">
-        <v>2.9805768</v>
+        <v>3.311751999999999</v>
       </c>
       <c r="N11">
-        <v>50.16608986666666</v>
+        <v>49.83491466666666</v>
       </c>
       <c r="O11">
-        <v>10.03321797333333</v>
+        <v>9.966982933333334</v>
       </c>
       <c r="P11">
-        <v>40.13287189333333</v>
+        <v>39.86793173333333</v>
       </c>
       <c r="Q11">
-        <v>44.05287189333333</v>
+        <v>43.78793173333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1045142607631547</v>
+        <v>0.1050457317816037</v>
       </c>
       <c r="T11">
-        <v>1.113787830415411</v>
+        <v>1.123869639244697</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.83100058574792</v>
+        <v>16.04790052717313</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09856515860344338</v>
+        <v>0.09840073991241594</v>
       </c>
       <c r="C12">
-        <v>578.6383428187862</v>
+        <v>573.9141181846619</v>
       </c>
       <c r="D12">
-        <v>594.9783428187862</v>
+        <v>596.8381181846619</v>
       </c>
       <c r="E12">
-        <v>-128.56</v>
+        <v>-121.976</v>
       </c>
       <c r="F12">
-        <v>65.84</v>
+        <v>72.42399999999999</v>
       </c>
       <c r="G12">
         <v>49.5</v>
@@ -2271,28 +2271,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M12">
-        <v>3.311752</v>
+        <v>3.642927199999999</v>
       </c>
       <c r="N12">
-        <v>49.83491466666666</v>
+        <v>49.50373946666666</v>
       </c>
       <c r="O12">
-        <v>9.966982933333334</v>
+        <v>9.900747893333332</v>
       </c>
       <c r="P12">
-        <v>39.86793173333333</v>
+        <v>39.60299157333333</v>
       </c>
       <c r="Q12">
-        <v>43.78793173333333</v>
+        <v>43.52299157333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1050457317816038</v>
+        <v>0.1055891459690067</v>
       </c>
       <c r="T12">
-        <v>1.123869639244697</v>
+        <v>1.134178005575765</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.04790052717313</v>
+        <v>14.5890004792483</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09840073991241594</v>
+        <v>0.09823632122138849</v>
       </c>
       <c r="C13">
-        <v>573.9141181846619</v>
+        <v>569.2015565285702</v>
       </c>
       <c r="D13">
-        <v>596.8381181846619</v>
+        <v>598.7095565285703</v>
       </c>
       <c r="E13">
-        <v>-121.976</v>
+        <v>-115.392</v>
       </c>
       <c r="F13">
-        <v>72.42399999999999</v>
+        <v>79.008</v>
       </c>
       <c r="G13">
         <v>49.5</v>
@@ -2353,28 +2353,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M13">
-        <v>3.642927199999999</v>
+        <v>3.9741024</v>
       </c>
       <c r="N13">
-        <v>49.50373946666666</v>
+        <v>49.17256426666666</v>
       </c>
       <c r="O13">
-        <v>9.900747893333332</v>
+        <v>9.834512853333333</v>
       </c>
       <c r="P13">
-        <v>39.60299157333333</v>
+        <v>39.33805141333333</v>
       </c>
       <c r="Q13">
-        <v>43.52299157333333</v>
+        <v>43.25805141333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1055891459690067</v>
+        <v>0.1061449104788506</v>
       </c>
       <c r="T13">
-        <v>1.134178005575765</v>
+        <v>1.144720652959812</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.5890004792483</v>
+        <v>13.37325043931094</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09823632122138849</v>
+        <v>0.09822790253036105</v>
       </c>
       <c r="C14">
-        <v>569.2015565285702</v>
+        <v>562.7136952357915</v>
       </c>
       <c r="D14">
-        <v>598.7095565285703</v>
+        <v>598.8056952357915</v>
       </c>
       <c r="E14">
-        <v>-115.392</v>
+        <v>-108.808</v>
       </c>
       <c r="F14">
-        <v>79.008</v>
+        <v>85.592</v>
       </c>
       <c r="G14">
         <v>49.5</v>
@@ -2435,45 +2435,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M14">
-        <v>3.9741024</v>
+        <v>4.433665599999999</v>
       </c>
       <c r="N14">
-        <v>49.17256426666666</v>
+        <v>48.71300106666666</v>
       </c>
       <c r="O14">
-        <v>9.834512853333333</v>
+        <v>9.742600213333333</v>
       </c>
       <c r="P14">
-        <v>39.33805141333333</v>
+        <v>38.97040085333333</v>
       </c>
       <c r="Q14">
-        <v>43.25805141333333</v>
+        <v>42.89040085333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1061449104788506</v>
+        <v>0.1067134511843231</v>
       </c>
       <c r="T14">
-        <v>1.144720652959812</v>
+        <v>1.155505660053837</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.37325043931094</v>
+        <v>11.98707152534613</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09822790253036105</v>
+        <v>0.09807548383933364</v>
       </c>
       <c r="C15">
-        <v>562.7136952357915</v>
+        <v>557.8756222659097</v>
       </c>
       <c r="D15">
-        <v>598.8056952357915</v>
+        <v>600.5516222659097</v>
       </c>
       <c r="E15">
-        <v>-108.808</v>
+        <v>-102.224</v>
       </c>
       <c r="F15">
-        <v>85.592</v>
+        <v>92.176</v>
       </c>
       <c r="G15">
         <v>49.5</v>
@@ -2517,28 +2517,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M15">
-        <v>4.433665599999999</v>
+        <v>4.7747168</v>
       </c>
       <c r="N15">
-        <v>48.71300106666666</v>
+        <v>48.37194986666666</v>
       </c>
       <c r="O15">
-        <v>9.742600213333333</v>
+        <v>9.674389973333334</v>
       </c>
       <c r="P15">
-        <v>38.97040085333333</v>
+        <v>38.69755989333333</v>
       </c>
       <c r="Q15">
-        <v>42.89040085333333</v>
+        <v>42.61755989333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1067134511843231</v>
+        <v>0.107295213766667</v>
       </c>
       <c r="T15">
-        <v>1.155505660053837</v>
+        <v>1.166541481266328</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.98707152534613</v>
+        <v>11.13085213067855</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09807548383933364</v>
+        <v>0.09792306514830618</v>
       </c>
       <c r="C16">
-        <v>557.8756222659097</v>
+        <v>553.047760204071</v>
       </c>
       <c r="D16">
-        <v>600.5516222659097</v>
+        <v>602.307760204071</v>
       </c>
       <c r="E16">
-        <v>-102.224</v>
+        <v>-95.64</v>
       </c>
       <c r="F16">
-        <v>92.176</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="G16">
         <v>49.5</v>
@@ -2599,28 +2599,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M16">
-        <v>4.7747168</v>
+        <v>5.115768</v>
       </c>
       <c r="N16">
-        <v>48.37194986666666</v>
+        <v>48.03089866666666</v>
       </c>
       <c r="O16">
-        <v>9.674389973333334</v>
+        <v>9.606179733333333</v>
       </c>
       <c r="P16">
-        <v>38.69755989333333</v>
+        <v>38.42471893333332</v>
       </c>
       <c r="Q16">
-        <v>42.61755989333333</v>
+        <v>42.34471893333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.107295213766667</v>
+        <v>0.1078906648803602</v>
       </c>
       <c r="T16">
-        <v>1.166541481266328</v>
+        <v>1.177836968860289</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.13085213067855</v>
+        <v>10.38879532196665</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09792306514830618</v>
+        <v>0.09798824645727874</v>
       </c>
       <c r="C17">
-        <v>553.047760204071</v>
+        <v>545.7114987107368</v>
       </c>
       <c r="D17">
-        <v>602.307760204071</v>
+        <v>601.5554987107369</v>
       </c>
       <c r="E17">
-        <v>-95.64000000000001</v>
+        <v>-89.05600000000001</v>
       </c>
       <c r="F17">
-        <v>98.75999999999999</v>
+        <v>105.344</v>
       </c>
       <c r="G17">
         <v>49.5</v>
@@ -2681,45 +2681,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M17">
-        <v>5.115767999999999</v>
+        <v>5.635903999999999</v>
       </c>
       <c r="N17">
-        <v>48.03089866666666</v>
+        <v>47.51076266666666</v>
       </c>
       <c r="O17">
-        <v>9.606179733333333</v>
+        <v>9.502152533333334</v>
       </c>
       <c r="P17">
-        <v>38.42471893333332</v>
+        <v>38.00861013333333</v>
       </c>
       <c r="Q17">
-        <v>42.34471893333333</v>
+        <v>41.92861013333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1078906648803602</v>
+        <v>0.1085002934015223</v>
       </c>
       <c r="T17">
-        <v>1.177836968860289</v>
+        <v>1.189401396635058</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.38879532196665</v>
+        <v>9.430016314448698</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09798824645727874</v>
+        <v>0.09784942776625132</v>
       </c>
       <c r="C18">
-        <v>545.7114987107368</v>
+        <v>540.7318803628541</v>
       </c>
       <c r="D18">
-        <v>601.5554987107369</v>
+        <v>603.1598803628541</v>
       </c>
       <c r="E18">
-        <v>-89.05600000000001</v>
+        <v>-82.47200000000001</v>
       </c>
       <c r="F18">
-        <v>105.344</v>
+        <v>111.928</v>
       </c>
       <c r="G18">
         <v>49.5</v>
@@ -2763,28 +2763,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M18">
-        <v>5.635903999999999</v>
+        <v>5.988148</v>
       </c>
       <c r="N18">
-        <v>47.51076266666666</v>
+        <v>47.15851866666666</v>
       </c>
       <c r="O18">
-        <v>9.502152533333334</v>
+        <v>9.431703733333332</v>
       </c>
       <c r="P18">
-        <v>38.00861013333333</v>
+        <v>37.72681493333333</v>
       </c>
       <c r="Q18">
-        <v>41.92861013333334</v>
+        <v>41.64681493333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1085002934015223</v>
+        <v>0.1091246117665678</v>
       </c>
       <c r="T18">
-        <v>1.189401396635058</v>
+        <v>1.201244485320063</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.430016314448698</v>
+        <v>8.875309472422302</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09784942776625132</v>
+        <v>0.09771060907522389</v>
       </c>
       <c r="C19">
-        <v>540.7318803628541</v>
+        <v>535.7608428490175</v>
       </c>
       <c r="D19">
-        <v>603.1598803628541</v>
+        <v>604.7728428490176</v>
       </c>
       <c r="E19">
-        <v>-82.47200000000001</v>
+        <v>-75.88799999999999</v>
       </c>
       <c r="F19">
-        <v>111.928</v>
+        <v>118.512</v>
       </c>
       <c r="G19">
         <v>49.5</v>
@@ -2845,28 +2845,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M19">
-        <v>5.988148</v>
+        <v>6.340392</v>
       </c>
       <c r="N19">
-        <v>47.15851866666666</v>
+        <v>46.80627466666666</v>
       </c>
       <c r="O19">
-        <v>9.431703733333332</v>
+        <v>9.361254933333333</v>
       </c>
       <c r="P19">
-        <v>37.72681493333333</v>
+        <v>37.44501973333333</v>
       </c>
       <c r="Q19">
-        <v>41.64681493333333</v>
+        <v>41.36501973333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1091246117665678</v>
+        <v>0.1097641574088096</v>
       </c>
       <c r="T19">
-        <v>1.201244485320063</v>
+        <v>1.213376429826654</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.875309472422302</v>
+        <v>8.382236723954396</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09771060907522389</v>
+        <v>0.09757179038419646</v>
       </c>
       <c r="C20">
-        <v>535.7608428490176</v>
+        <v>530.7984551940847</v>
       </c>
       <c r="D20">
-        <v>604.7728428490176</v>
+        <v>606.3944551940847</v>
       </c>
       <c r="E20">
-        <v>-75.88800000000002</v>
+        <v>-69.304</v>
       </c>
       <c r="F20">
-        <v>118.512</v>
+        <v>125.096</v>
       </c>
       <c r="G20">
         <v>49.5</v>
@@ -2927,28 +2927,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M20">
-        <v>6.340391999999999</v>
+        <v>6.692636</v>
       </c>
       <c r="N20">
-        <v>46.80627466666666</v>
+        <v>46.45403066666666</v>
       </c>
       <c r="O20">
-        <v>9.361254933333333</v>
+        <v>9.290806133333332</v>
       </c>
       <c r="P20">
-        <v>37.44501973333333</v>
+        <v>37.16322453333333</v>
       </c>
       <c r="Q20">
-        <v>41.36501973333333</v>
+        <v>41.08322453333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1097641574088096</v>
+        <v>0.1104194943014771</v>
       </c>
       <c r="T20">
-        <v>1.213376429826654</v>
+        <v>1.225807928518593</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.382236723954398</v>
+        <v>7.941066370062059</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09757179038419646</v>
+        <v>0.09756097169316902</v>
       </c>
       <c r="C21">
-        <v>530.7984551940847</v>
+        <v>524.3411992260628</v>
       </c>
       <c r="D21">
-        <v>606.3944551940847</v>
+        <v>606.5211992260628</v>
       </c>
       <c r="E21">
-        <v>-69.304</v>
+        <v>-62.72</v>
       </c>
       <c r="F21">
-        <v>125.096</v>
+        <v>131.68</v>
       </c>
       <c r="G21">
         <v>49.5</v>
@@ -3009,45 +3009,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M21">
-        <v>6.692636</v>
+        <v>7.150224000000001</v>
       </c>
       <c r="N21">
-        <v>46.45403066666666</v>
+        <v>45.99644266666666</v>
       </c>
       <c r="O21">
-        <v>9.290806133333332</v>
+        <v>9.199288533333332</v>
       </c>
       <c r="P21">
-        <v>37.16322453333333</v>
+        <v>36.79715413333333</v>
       </c>
       <c r="Q21">
-        <v>41.08322453333333</v>
+        <v>40.71715413333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1104194943014771</v>
+        <v>0.1110912146164613</v>
       </c>
       <c r="T21">
-        <v>1.225807928518593</v>
+        <v>1.238550214677829</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.941066370062059</v>
+        <v>7.432867371241328</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09756097169316902</v>
+        <v>0.09742855300214158</v>
       </c>
       <c r="C22">
-        <v>524.3411992260628</v>
+        <v>519.3128256887795</v>
       </c>
       <c r="D22">
-        <v>606.5211992260628</v>
+        <v>608.0768256887795</v>
       </c>
       <c r="E22">
-        <v>-62.72</v>
+        <v>-56.136</v>
       </c>
       <c r="F22">
-        <v>131.68</v>
+        <v>138.264</v>
       </c>
       <c r="G22">
         <v>49.5</v>
@@ -3091,28 +3091,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M22">
-        <v>7.150224000000001</v>
+        <v>7.507735200000001</v>
       </c>
       <c r="N22">
-        <v>45.99644266666666</v>
+        <v>45.63893146666666</v>
       </c>
       <c r="O22">
-        <v>9.199288533333332</v>
+        <v>9.127786293333333</v>
       </c>
       <c r="P22">
-        <v>36.79715413333333</v>
+        <v>36.51114517333333</v>
       </c>
       <c r="Q22">
-        <v>40.71715413333333</v>
+        <v>40.43114517333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1110912146164613</v>
+        <v>0.11177994050904</v>
       </c>
       <c r="T22">
-        <v>1.238550214677829</v>
+        <v>1.251615090360085</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.432867371241328</v>
+        <v>7.078921305944123</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09742855300214158</v>
+        <v>0.09729613431111414</v>
       </c>
       <c r="C23">
-        <v>519.3128256887795</v>
+        <v>514.2924525197833</v>
       </c>
       <c r="D23">
-        <v>608.0768256887795</v>
+        <v>609.6404525197833</v>
       </c>
       <c r="E23">
-        <v>-56.13600000000002</v>
+        <v>-49.55200000000002</v>
       </c>
       <c r="F23">
-        <v>138.264</v>
+        <v>144.848</v>
       </c>
       <c r="G23">
         <v>49.5</v>
@@ -3173,28 +3173,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M23">
-        <v>7.507735199999999</v>
+        <v>7.865246399999999</v>
       </c>
       <c r="N23">
-        <v>45.63893146666666</v>
+        <v>45.28142026666666</v>
       </c>
       <c r="O23">
-        <v>9.127786293333333</v>
+        <v>9.056284053333334</v>
       </c>
       <c r="P23">
-        <v>36.51114517333333</v>
+        <v>36.22513621333333</v>
       </c>
       <c r="Q23">
-        <v>40.43114517333333</v>
+        <v>40.14513621333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.11177994050904</v>
+        <v>0.1124863260398899</v>
       </c>
       <c r="T23">
-        <v>1.251615090360085</v>
+        <v>1.265014962854706</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.078921305944124</v>
+        <v>6.757152155673936</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09729613431111414</v>
+        <v>0.09716371562008673</v>
       </c>
       <c r="C24">
-        <v>514.2924525197833</v>
+        <v>509.2801415953387</v>
       </c>
       <c r="D24">
-        <v>609.6404525197833</v>
+        <v>611.2121415953387</v>
       </c>
       <c r="E24">
-        <v>-49.55200000000002</v>
+        <v>-42.96800000000002</v>
       </c>
       <c r="F24">
-        <v>144.848</v>
+        <v>151.432</v>
       </c>
       <c r="G24">
         <v>49.5</v>
@@ -3255,28 +3255,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M24">
-        <v>7.865246399999999</v>
+        <v>8.2227576</v>
       </c>
       <c r="N24">
-        <v>45.28142026666666</v>
+        <v>44.92390906666666</v>
       </c>
       <c r="O24">
-        <v>9.056284053333334</v>
+        <v>8.984781813333333</v>
       </c>
       <c r="P24">
-        <v>36.22513621333333</v>
+        <v>35.93912725333333</v>
       </c>
       <c r="Q24">
-        <v>40.14513621333333</v>
+        <v>39.85912725333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1124863260398899</v>
+        <v>0.1132110592468659</v>
       </c>
       <c r="T24">
-        <v>1.265014962854706</v>
+        <v>1.278762883985551</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.757152155673936</v>
+        <v>6.463362931514199</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09716371562008673</v>
+        <v>0.09703129692905928</v>
       </c>
       <c r="C25">
-        <v>509.2801415953387</v>
+        <v>504.2759554314438</v>
       </c>
       <c r="D25">
-        <v>611.2121415953387</v>
+        <v>612.7919554314439</v>
       </c>
       <c r="E25">
-        <v>-42.96800000000002</v>
+        <v>-36.38399999999999</v>
       </c>
       <c r="F25">
-        <v>151.432</v>
+        <v>158.016</v>
       </c>
       <c r="G25">
         <v>49.5</v>
@@ -3337,28 +3337,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M25">
-        <v>8.2227576</v>
+        <v>8.580268800000001</v>
       </c>
       <c r="N25">
-        <v>44.92390906666666</v>
+        <v>44.56639786666666</v>
       </c>
       <c r="O25">
-        <v>8.984781813333333</v>
+        <v>8.913279573333332</v>
       </c>
       <c r="P25">
-        <v>35.93912725333333</v>
+        <v>35.65311829333333</v>
       </c>
       <c r="Q25">
-        <v>39.85912725333333</v>
+        <v>39.57311829333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1132110592468659</v>
+        <v>0.1139548643803411</v>
       </c>
       <c r="T25">
-        <v>1.278762883985551</v>
+        <v>1.292872592514576</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.463362931514199</v>
+        <v>6.194056142701108</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09703129692905928</v>
+        <v>0.09709887823803183</v>
       </c>
       <c r="C26">
-        <v>504.2759554314439</v>
+        <v>496.884661317063</v>
       </c>
       <c r="D26">
-        <v>612.7919554314439</v>
+        <v>611.984661317063</v>
       </c>
       <c r="E26">
-        <v>-36.38400000000001</v>
+        <v>-29.80000000000001</v>
       </c>
       <c r="F26">
-        <v>158.016</v>
+        <v>164.6</v>
       </c>
       <c r="G26">
         <v>49.5</v>
@@ -3419,45 +3419,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M26">
-        <v>8.580268799999999</v>
+        <v>9.10238</v>
       </c>
       <c r="N26">
-        <v>44.56639786666666</v>
+        <v>44.04428666666666</v>
       </c>
       <c r="O26">
-        <v>8.913279573333332</v>
+        <v>8.808857333333334</v>
       </c>
       <c r="P26">
-        <v>35.65311829333333</v>
+        <v>35.23542933333333</v>
       </c>
       <c r="Q26">
-        <v>39.57311829333333</v>
+        <v>39.15542933333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1139548643803411</v>
+        <v>0.1147185043173758</v>
       </c>
       <c r="T26">
-        <v>1.292872592514576</v>
+        <v>1.307358559937709</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.194056142701108</v>
+        <v>5.83876597842176</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09709887823803183</v>
+        <v>0.0969744595470044</v>
       </c>
       <c r="C27">
-        <v>496.884661317063</v>
+        <v>491.7885584275346</v>
       </c>
       <c r="D27">
-        <v>611.984661317063</v>
+        <v>613.4725584275345</v>
       </c>
       <c r="E27">
-        <v>-29.80000000000001</v>
+        <v>-23.21600000000001</v>
       </c>
       <c r="F27">
-        <v>164.6</v>
+        <v>171.184</v>
       </c>
       <c r="G27">
         <v>49.5</v>
@@ -3501,28 +3501,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M27">
-        <v>9.10238</v>
+        <v>9.4664752</v>
       </c>
       <c r="N27">
-        <v>44.04428666666666</v>
+        <v>43.68019146666666</v>
       </c>
       <c r="O27">
-        <v>8.808857333333334</v>
+        <v>8.736038293333333</v>
       </c>
       <c r="P27">
-        <v>35.23542933333333</v>
+        <v>34.94415317333333</v>
       </c>
       <c r="Q27">
-        <v>39.15542933333333</v>
+        <v>38.86415317333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1147185043173758</v>
+        <v>0.1155027831716276</v>
       </c>
       <c r="T27">
-        <v>1.307358559937709</v>
+        <v>1.322236039993899</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.83876597842176</v>
+        <v>5.61419805617477</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0969744595470044</v>
+        <v>0.09685004085597697</v>
       </c>
       <c r="C28">
-        <v>491.7885584275346</v>
+        <v>486.699708116369</v>
       </c>
       <c r="D28">
-        <v>613.4725584275345</v>
+        <v>614.9677081163691</v>
       </c>
       <c r="E28">
-        <v>-23.21600000000001</v>
+        <v>-16.63200000000001</v>
       </c>
       <c r="F28">
-        <v>171.184</v>
+        <v>177.768</v>
       </c>
       <c r="G28">
         <v>49.5</v>
@@ -3583,28 +3583,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M28">
-        <v>9.4664752</v>
+        <v>9.830570400000001</v>
       </c>
       <c r="N28">
-        <v>43.68019146666666</v>
+        <v>43.31609626666666</v>
       </c>
       <c r="O28">
-        <v>8.736038293333333</v>
+        <v>8.663219253333333</v>
       </c>
       <c r="P28">
-        <v>34.94415317333333</v>
+        <v>34.65287701333333</v>
       </c>
       <c r="Q28">
-        <v>38.86415317333334</v>
+        <v>38.57287701333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1155027831716276</v>
+        <v>0.1163085491177767</v>
       </c>
       <c r="T28">
-        <v>1.322236039993899</v>
+        <v>1.337521122243409</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.61419805617477</v>
+        <v>5.406264794834962</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09685004085597697</v>
+        <v>0.09672562216494954</v>
       </c>
       <c r="C29">
-        <v>486.699708116369</v>
+        <v>481.6181635408733</v>
       </c>
       <c r="D29">
-        <v>614.9677081163691</v>
+        <v>616.4701635408733</v>
       </c>
       <c r="E29">
-        <v>-16.63200000000001</v>
+        <v>-10.048</v>
       </c>
       <c r="F29">
-        <v>177.768</v>
+        <v>184.352</v>
       </c>
       <c r="G29">
         <v>49.5</v>
@@ -3665,28 +3665,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M29">
-        <v>9.830570400000001</v>
+        <v>10.1946656</v>
       </c>
       <c r="N29">
-        <v>43.31609626666666</v>
+        <v>42.95200106666666</v>
       </c>
       <c r="O29">
-        <v>8.663219253333333</v>
+        <v>8.590400213333332</v>
       </c>
       <c r="P29">
-        <v>34.65287701333333</v>
+        <v>34.36160085333333</v>
       </c>
       <c r="Q29">
-        <v>38.57287701333333</v>
+        <v>38.28160085333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1163085491177767</v>
+        <v>0.1171366974513188</v>
       </c>
       <c r="T29">
-        <v>1.337521122243409</v>
+        <v>1.353230790110962</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.406264794834962</v>
+        <v>5.213183909305143</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09672562216494954</v>
+        <v>0.09660120347392209</v>
       </c>
       <c r="C30">
-        <v>481.6181635408733</v>
+        <v>476.5439783791103</v>
       </c>
       <c r="D30">
-        <v>616.4701635408733</v>
+        <v>617.9799783791103</v>
       </c>
       <c r="E30">
-        <v>-10.048</v>
+        <v>-3.463999999999999</v>
       </c>
       <c r="F30">
-        <v>184.352</v>
+        <v>190.936</v>
       </c>
       <c r="G30">
         <v>49.5</v>
@@ -3747,28 +3747,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M30">
-        <v>10.1946656</v>
+        <v>10.5587608</v>
       </c>
       <c r="N30">
-        <v>42.95200106666666</v>
+        <v>42.58790586666666</v>
       </c>
       <c r="O30">
-        <v>8.590400213333332</v>
+        <v>8.517581173333332</v>
       </c>
       <c r="P30">
-        <v>34.36160085333333</v>
+        <v>34.07032469333333</v>
       </c>
       <c r="Q30">
-        <v>38.28160085333333</v>
+        <v>37.99032469333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1171366974513188</v>
+        <v>0.1179881739069325</v>
       </c>
       <c r="T30">
-        <v>1.353230790110962</v>
+        <v>1.369382983833938</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.213183909305143</v>
+        <v>5.033418946915311</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09660120347392209</v>
+        <v>0.09647678478289466</v>
       </c>
       <c r="C31">
-        <v>476.5439783791103</v>
+        <v>471.4772068362923</v>
       </c>
       <c r="D31">
-        <v>617.9799783791103</v>
+        <v>619.4972068362923</v>
       </c>
       <c r="E31">
-        <v>-3.464000000000027</v>
+        <v>3.119999999999976</v>
       </c>
       <c r="F31">
-        <v>190.936</v>
+        <v>197.52</v>
       </c>
       <c r="G31">
         <v>49.5</v>
@@ -3829,28 +3829,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M31">
-        <v>10.5587608</v>
+        <v>10.922856</v>
       </c>
       <c r="N31">
-        <v>42.58790586666666</v>
+        <v>42.22381066666667</v>
       </c>
       <c r="O31">
-        <v>8.517581173333332</v>
+        <v>8.444762133333333</v>
       </c>
       <c r="P31">
-        <v>34.07032469333333</v>
+        <v>33.77904853333333</v>
       </c>
       <c r="Q31">
-        <v>37.99032469333333</v>
+        <v>37.69904853333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1179881739069325</v>
+        <v>0.1188639782612781</v>
       </c>
       <c r="T31">
-        <v>1.369382983833938</v>
+        <v>1.385996668806142</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.033418946915311</v>
+        <v>4.865638315351467</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09647678478289466</v>
+        <v>0.09635236609186722</v>
       </c>
       <c r="C32">
-        <v>471.4772068362923</v>
+        <v>466.4179036512674</v>
       </c>
       <c r="D32">
-        <v>619.4972068362923</v>
+        <v>621.0219036512674</v>
       </c>
       <c r="E32">
-        <v>3.119999999999976</v>
+        <v>9.703999999999979</v>
       </c>
       <c r="F32">
-        <v>197.52</v>
+        <v>204.104</v>
       </c>
       <c r="G32">
         <v>49.5</v>
@@ -3911,28 +3911,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M32">
-        <v>10.922856</v>
+        <v>11.2869512</v>
       </c>
       <c r="N32">
-        <v>42.22381066666667</v>
+        <v>41.85971546666666</v>
       </c>
       <c r="O32">
-        <v>8.444762133333333</v>
+        <v>8.371943093333334</v>
       </c>
       <c r="P32">
-        <v>33.77904853333333</v>
+        <v>33.48777237333333</v>
       </c>
       <c r="Q32">
-        <v>37.69904853333333</v>
+        <v>37.40777237333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1188639782612781</v>
+        <v>0.1197651682490829</v>
       </c>
       <c r="T32">
-        <v>1.385996668806142</v>
+        <v>1.403091909864497</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.865638315351467</v>
+        <v>4.708682240662711</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09635236609186722</v>
+        <v>0.09622794740083977</v>
       </c>
       <c r="C33">
-        <v>466.4179036512674</v>
+        <v>461.3661241031031</v>
       </c>
       <c r="D33">
-        <v>621.0219036512674</v>
+        <v>622.554124103103</v>
       </c>
       <c r="E33">
-        <v>9.703999999999979</v>
+        <v>16.28799999999998</v>
       </c>
       <c r="F33">
-        <v>204.104</v>
+        <v>210.688</v>
       </c>
       <c r="G33">
         <v>49.5</v>
@@ -3993,28 +3993,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M33">
-        <v>11.2869512</v>
+        <v>11.6510464</v>
       </c>
       <c r="N33">
-        <v>41.85971546666666</v>
+        <v>41.49562026666666</v>
       </c>
       <c r="O33">
-        <v>8.371943093333334</v>
+        <v>8.299124053333333</v>
       </c>
       <c r="P33">
-        <v>33.48777237333333</v>
+        <v>33.19649621333333</v>
       </c>
       <c r="Q33">
-        <v>37.40777237333333</v>
+        <v>37.11649621333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1197651682490829</v>
+        <v>0.1206928638247644</v>
       </c>
       <c r="T33">
-        <v>1.403091909864497</v>
+        <v>1.420689952130451</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.708682240662711</v>
+        <v>4.561535920642</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09622794740083977</v>
+        <v>0.09676352870981235</v>
       </c>
       <c r="C34">
-        <v>461.3661241031031</v>
+        <v>448.2396345790365</v>
       </c>
       <c r="D34">
-        <v>622.554124103103</v>
+        <v>616.0116345790365</v>
       </c>
       <c r="E34">
-        <v>16.28799999999998</v>
+        <v>22.87199999999999</v>
       </c>
       <c r="F34">
-        <v>210.688</v>
+        <v>217.272</v>
       </c>
       <c r="G34">
         <v>49.5</v>
@@ -4075,45 +4075,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M34">
-        <v>11.6510464</v>
+        <v>12.5583216</v>
       </c>
       <c r="N34">
-        <v>41.49562026666666</v>
+        <v>40.58834506666666</v>
       </c>
       <c r="O34">
-        <v>8.299124053333333</v>
+        <v>8.117669013333332</v>
       </c>
       <c r="P34">
-        <v>33.19649621333333</v>
+        <v>32.47067605333333</v>
       </c>
       <c r="Q34">
-        <v>37.11649621333333</v>
+        <v>36.39067605333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1206928638247644</v>
+        <v>0.1216482518056901</v>
       </c>
       <c r="T34">
-        <v>1.420689952130451</v>
+        <v>1.438813309090911</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.561535920642</v>
+        <v>4.231988028294056</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09676352870981235</v>
+        <v>0.09665911001878491</v>
       </c>
       <c r="C35">
-        <v>448.2396345790365</v>
+        <v>442.9203662763994</v>
       </c>
       <c r="D35">
-        <v>616.0116345790365</v>
+        <v>617.2763662763994</v>
       </c>
       <c r="E35">
-        <v>22.87199999999999</v>
+        <v>29.45599999999999</v>
       </c>
       <c r="F35">
-        <v>217.272</v>
+        <v>223.856</v>
       </c>
       <c r="G35">
         <v>49.5</v>
@@ -4157,28 +4157,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M35">
-        <v>12.5583216</v>
+        <v>12.9388768</v>
       </c>
       <c r="N35">
-        <v>40.58834506666666</v>
+        <v>40.20778986666666</v>
       </c>
       <c r="O35">
-        <v>8.117669013333332</v>
+        <v>8.041557973333331</v>
       </c>
       <c r="P35">
-        <v>32.47067605333333</v>
+        <v>32.16623189333333</v>
       </c>
       <c r="Q35">
-        <v>36.39067605333333</v>
+        <v>36.08623189333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1216482518056901</v>
+        <v>0.1226325909375529</v>
       </c>
       <c r="T35">
-        <v>1.438813309090911</v>
+        <v>1.457485858686536</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.231988028294056</v>
+        <v>4.10751779216776</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09665911001878491</v>
+        <v>0.09753469132775748</v>
       </c>
       <c r="C36">
-        <v>442.9203662763994</v>
+        <v>425.8893019388927</v>
       </c>
       <c r="D36">
-        <v>617.2763662763994</v>
+        <v>606.8293019388927</v>
       </c>
       <c r="E36">
-        <v>29.45599999999999</v>
+        <v>36.04000000000002</v>
       </c>
       <c r="F36">
-        <v>223.856</v>
+        <v>230.44</v>
       </c>
       <c r="G36">
         <v>49.5</v>
@@ -4239,45 +4239,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M36">
-        <v>12.9388768</v>
+        <v>14.125972</v>
       </c>
       <c r="N36">
-        <v>40.20778986666666</v>
+        <v>39.02069466666666</v>
       </c>
       <c r="O36">
-        <v>8.041557973333331</v>
+        <v>7.804138933333332</v>
       </c>
       <c r="P36">
-        <v>32.16623189333333</v>
+        <v>31.21655573333333</v>
       </c>
       <c r="Q36">
-        <v>36.08623189333333</v>
+        <v>35.13655573333332</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1226325909375529</v>
+        <v>0.1236472174273192</v>
       </c>
       <c r="T36">
-        <v>1.457485858686536</v>
+        <v>1.47673294826972</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.10751779216776</v>
+        <v>3.762336968151052</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09753469132775748</v>
+        <v>0.09745827263673004</v>
       </c>
       <c r="C37">
-        <v>425.8893019388927</v>
+        <v>420.2029916711331</v>
       </c>
       <c r="D37">
-        <v>606.8293019388927</v>
+        <v>607.7269916711331</v>
       </c>
       <c r="E37">
-        <v>36.04000000000002</v>
+        <v>42.62400000000002</v>
       </c>
       <c r="F37">
-        <v>230.44</v>
+        <v>237.024</v>
       </c>
       <c r="G37">
         <v>49.5</v>
@@ -4321,28 +4321,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M37">
-        <v>14.125972</v>
+        <v>14.5295712</v>
       </c>
       <c r="N37">
-        <v>39.02069466666666</v>
+        <v>38.61709546666666</v>
       </c>
       <c r="O37">
-        <v>7.804138933333332</v>
+        <v>7.723419093333333</v>
       </c>
       <c r="P37">
-        <v>31.21655573333333</v>
+        <v>30.89367637333333</v>
       </c>
       <c r="Q37">
-        <v>35.13655573333332</v>
+        <v>34.81367637333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1236472174273192</v>
+        <v>0.1246935509948907</v>
       </c>
       <c r="T37">
-        <v>1.47673294826972</v>
+        <v>1.496581509402377</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.762336968151052</v>
+        <v>3.657827607924634</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09745827263673004</v>
+        <v>0.09738185394570262</v>
       </c>
       <c r="C38">
-        <v>420.2029916711331</v>
+        <v>414.5193412641204</v>
       </c>
       <c r="D38">
-        <v>607.7269916711331</v>
+        <v>608.6273412641203</v>
       </c>
       <c r="E38">
-        <v>42.62399999999997</v>
+        <v>49.20799999999997</v>
       </c>
       <c r="F38">
-        <v>237.024</v>
+        <v>243.608</v>
       </c>
       <c r="G38">
         <v>49.5</v>
@@ -4403,28 +4403,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M38">
-        <v>14.5295712</v>
+        <v>14.9331704</v>
       </c>
       <c r="N38">
-        <v>38.61709546666666</v>
+        <v>38.21349626666667</v>
       </c>
       <c r="O38">
-        <v>7.723419093333333</v>
+        <v>7.642699253333333</v>
       </c>
       <c r="P38">
-        <v>30.89367637333333</v>
+        <v>30.57079701333333</v>
       </c>
       <c r="Q38">
-        <v>34.81367637333333</v>
+        <v>34.49079701333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1246935509948907</v>
+        <v>0.1257731015011153</v>
       </c>
       <c r="T38">
-        <v>1.496581509402377</v>
+        <v>1.517060183586865</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.657827607924635</v>
+        <v>3.558967402305051</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09738185394570262</v>
+        <v>0.09815663525467518</v>
       </c>
       <c r="C39">
-        <v>414.5193412641204</v>
+        <v>398.928782957855</v>
       </c>
       <c r="D39">
-        <v>608.6273412641203</v>
+        <v>599.620782957855</v>
       </c>
       <c r="E39">
-        <v>49.20799999999997</v>
+        <v>55.792</v>
       </c>
       <c r="F39">
-        <v>243.608</v>
+        <v>250.192</v>
       </c>
       <c r="G39">
         <v>49.5</v>
@@ -4485,45 +4485,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M39">
-        <v>14.9331704</v>
+        <v>16.0373072</v>
       </c>
       <c r="N39">
-        <v>38.21349626666667</v>
+        <v>37.10935946666666</v>
       </c>
       <c r="O39">
-        <v>7.642699253333333</v>
+        <v>7.421871893333332</v>
       </c>
       <c r="P39">
-        <v>30.57079701333333</v>
+        <v>29.68748757333333</v>
       </c>
       <c r="Q39">
-        <v>34.49079701333334</v>
+        <v>33.60748757333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1257731015011153</v>
+        <v>0.126887476217218</v>
       </c>
       <c r="T39">
-        <v>1.517060183586865</v>
+        <v>1.538199460164401</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.558967402305051</v>
+        <v>3.31393955380905</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09815663525467518</v>
+        <v>0.09810261656364774</v>
       </c>
       <c r="C40">
-        <v>398.928782957855</v>
+        <v>392.9640775923559</v>
       </c>
       <c r="D40">
-        <v>599.620782957855</v>
+        <v>600.2400775923559</v>
       </c>
       <c r="E40">
-        <v>55.792</v>
+        <v>62.376</v>
       </c>
       <c r="F40">
-        <v>250.192</v>
+        <v>256.776</v>
       </c>
       <c r="G40">
         <v>49.5</v>
@@ -4567,28 +4567,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M40">
-        <v>16.0373072</v>
+        <v>16.4593416</v>
       </c>
       <c r="N40">
-        <v>37.10935946666666</v>
+        <v>36.68732506666666</v>
       </c>
       <c r="O40">
-        <v>7.421871893333332</v>
+        <v>7.337465013333333</v>
       </c>
       <c r="P40">
-        <v>29.68748757333333</v>
+        <v>29.34986005333333</v>
       </c>
       <c r="Q40">
-        <v>33.60748757333333</v>
+        <v>33.26986005333332</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.126887476217218</v>
+        <v>0.1280383878092586</v>
       </c>
       <c r="T40">
-        <v>1.538199460164401</v>
+        <v>1.560031827777266</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.31393955380905</v>
+        <v>3.228966744737022</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09810261656364774</v>
+        <v>0.09804859787262031</v>
       </c>
       <c r="C41">
-        <v>392.9640775923559</v>
+        <v>387.0006527774125</v>
       </c>
       <c r="D41">
-        <v>600.2400775923559</v>
+        <v>600.8606527774125</v>
       </c>
       <c r="E41">
-        <v>62.376</v>
+        <v>68.96000000000001</v>
       </c>
       <c r="F41">
-        <v>256.776</v>
+        <v>263.36</v>
       </c>
       <c r="G41">
         <v>49.5</v>
@@ -4649,28 +4649,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M41">
-        <v>16.4593416</v>
+        <v>16.881376</v>
       </c>
       <c r="N41">
-        <v>36.68732506666666</v>
+        <v>36.26529066666666</v>
       </c>
       <c r="O41">
-        <v>7.337465013333333</v>
+        <v>7.253058133333332</v>
       </c>
       <c r="P41">
-        <v>29.34986005333333</v>
+        <v>29.01223253333333</v>
       </c>
       <c r="Q41">
-        <v>33.26986005333332</v>
+        <v>32.93223253333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1280383878092586</v>
+        <v>0.1292276631210338</v>
       </c>
       <c r="T41">
-        <v>1.560031827777266</v>
+        <v>1.582591940977226</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.228966744737022</v>
+        <v>3.148242576118597</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09804859787262031</v>
+        <v>0.09799457918159288</v>
       </c>
       <c r="C42">
-        <v>387.0006527774125</v>
+        <v>381.0385124889353</v>
       </c>
       <c r="D42">
-        <v>600.8606527774125</v>
+        <v>601.4825124889353</v>
       </c>
       <c r="E42">
-        <v>68.96000000000001</v>
+        <v>75.54400000000001</v>
       </c>
       <c r="F42">
-        <v>263.36</v>
+        <v>269.944</v>
       </c>
       <c r="G42">
         <v>49.5</v>
@@ -4731,28 +4731,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M42">
-        <v>16.881376</v>
+        <v>17.3034104</v>
       </c>
       <c r="N42">
-        <v>36.26529066666666</v>
+        <v>35.84325626666666</v>
       </c>
       <c r="O42">
-        <v>7.253058133333332</v>
+        <v>7.168651253333332</v>
       </c>
       <c r="P42">
-        <v>29.01223253333333</v>
+        <v>28.67460501333333</v>
       </c>
       <c r="Q42">
-        <v>32.93223253333333</v>
+        <v>32.59460501333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1292276631210338</v>
+        <v>0.1304572528501574</v>
       </c>
       <c r="T42">
-        <v>1.582591940977226</v>
+        <v>1.605916803777186</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.148242576118597</v>
+        <v>3.071456171823022</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09799457918159288</v>
+        <v>0.1005613604905655</v>
       </c>
       <c r="C43">
-        <v>381.0385124889353</v>
+        <v>346.2617492540546</v>
       </c>
       <c r="D43">
-        <v>601.4825124889353</v>
+        <v>573.2897492540546</v>
       </c>
       <c r="E43">
-        <v>75.54400000000001</v>
+        <v>82.12800000000001</v>
       </c>
       <c r="F43">
-        <v>269.944</v>
+        <v>276.528</v>
       </c>
       <c r="G43">
         <v>49.5</v>
@@ -4813,45 +4813,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M43">
-        <v>17.3034104</v>
+        <v>19.8823632</v>
       </c>
       <c r="N43">
-        <v>35.84325626666666</v>
+        <v>33.26430346666666</v>
       </c>
       <c r="O43">
-        <v>7.168651253333332</v>
+        <v>6.652860693333333</v>
       </c>
       <c r="P43">
-        <v>28.67460501333333</v>
+        <v>26.61144277333333</v>
       </c>
       <c r="Q43">
-        <v>32.59460501333333</v>
+        <v>30.53144277333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1304572528501574</v>
+        <v>0.1317292422251128</v>
       </c>
       <c r="T43">
-        <v>1.605916803777186</v>
+        <v>1.630045972190937</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.071456171823022</v>
+        <v>2.673055819977509</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1005613604905654</v>
+        <v>0.100569741799538</v>
       </c>
       <c r="C44">
-        <v>346.2617492540548</v>
+        <v>339.59001981876</v>
       </c>
       <c r="D44">
-        <v>573.2897492540548</v>
+        <v>573.2020198187599</v>
       </c>
       <c r="E44">
-        <v>82.12799999999996</v>
+        <v>88.71199999999996</v>
       </c>
       <c r="F44">
-        <v>276.528</v>
+        <v>283.112</v>
       </c>
       <c r="G44">
         <v>49.5</v>
@@ -4895,28 +4895,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M44">
-        <v>19.8823632</v>
+        <v>20.3557528</v>
       </c>
       <c r="N44">
-        <v>33.26430346666666</v>
+        <v>32.79091386666666</v>
       </c>
       <c r="O44">
-        <v>6.652860693333333</v>
+        <v>6.558182773333333</v>
       </c>
       <c r="P44">
-        <v>26.61144277333333</v>
+        <v>26.23273109333333</v>
       </c>
       <c r="Q44">
-        <v>30.53144277333333</v>
+        <v>30.15273109333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1317292422251128</v>
+        <v>0.133045862806207</v>
       </c>
       <c r="T44">
-        <v>1.630045972190936</v>
+        <v>1.655021778092889</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.67305581997751</v>
+        <v>2.610891731140824</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.100569741799538</v>
+        <v>0.1005781231085106</v>
       </c>
       <c r="C45">
-        <v>339.59001981876</v>
+        <v>332.9183172294932</v>
       </c>
       <c r="D45">
-        <v>573.2020198187599</v>
+        <v>573.1143172294932</v>
       </c>
       <c r="E45">
-        <v>88.71199999999996</v>
+        <v>95.29599999999996</v>
       </c>
       <c r="F45">
-        <v>283.112</v>
+        <v>289.696</v>
       </c>
       <c r="G45">
         <v>49.5</v>
@@ -4977,28 +4977,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M45">
-        <v>20.3557528</v>
+        <v>20.8291424</v>
       </c>
       <c r="N45">
-        <v>32.79091386666666</v>
+        <v>32.31752426666667</v>
       </c>
       <c r="O45">
-        <v>6.558182773333333</v>
+        <v>6.463504853333333</v>
       </c>
       <c r="P45">
-        <v>26.23273109333333</v>
+        <v>25.85401941333333</v>
       </c>
       <c r="Q45">
-        <v>30.15273109333333</v>
+        <v>29.77401941333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.133045862806207</v>
+        <v>0.1344095055509117</v>
       </c>
       <c r="T45">
-        <v>1.655021778092889</v>
+        <v>1.680889577062768</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.610891731140824</v>
+        <v>2.551553282705805</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1005781231085106</v>
+        <v>0.1019905044174831</v>
       </c>
       <c r="C46">
-        <v>332.9183172294932</v>
+        <v>311.928752482371</v>
       </c>
       <c r="D46">
-        <v>573.1143172294932</v>
+        <v>558.708752482371</v>
       </c>
       <c r="E46">
-        <v>95.29599999999996</v>
+        <v>101.88</v>
       </c>
       <c r="F46">
-        <v>289.696</v>
+        <v>296.28</v>
       </c>
       <c r="G46">
         <v>49.5</v>
@@ -5059,45 +5059,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M46">
-        <v>20.8291424</v>
+        <v>22.458024</v>
       </c>
       <c r="N46">
-        <v>32.31752426666667</v>
+        <v>30.68864266666666</v>
       </c>
       <c r="O46">
-        <v>6.463504853333333</v>
+        <v>6.137728533333333</v>
       </c>
       <c r="P46">
-        <v>25.85401941333333</v>
+        <v>24.55091413333333</v>
       </c>
       <c r="Q46">
-        <v>29.77401941333333</v>
+        <v>28.47091413333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1344095055509117</v>
+        <v>0.1358227353045148</v>
       </c>
       <c r="T46">
-        <v>1.680889577062768</v>
+        <v>1.707698023267916</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.551553282705805</v>
+        <v>2.366488995944909</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1019905044174831</v>
+        <v>0.1020300857264557</v>
       </c>
       <c r="C47">
-        <v>311.928752482371</v>
+        <v>304.9514679359939</v>
       </c>
       <c r="D47">
-        <v>558.708752482371</v>
+        <v>558.3154679359939</v>
       </c>
       <c r="E47">
-        <v>101.88</v>
+        <v>108.464</v>
       </c>
       <c r="F47">
-        <v>296.28</v>
+        <v>302.864</v>
       </c>
       <c r="G47">
         <v>49.5</v>
@@ -5141,28 +5141,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M47">
-        <v>22.458024</v>
+        <v>22.9570912</v>
       </c>
       <c r="N47">
-        <v>30.68864266666666</v>
+        <v>30.18957546666666</v>
       </c>
       <c r="O47">
-        <v>6.137728533333333</v>
+        <v>6.037915093333332</v>
       </c>
       <c r="P47">
-        <v>24.55091413333333</v>
+        <v>24.15166037333333</v>
       </c>
       <c r="Q47">
-        <v>28.47091413333333</v>
+        <v>28.07166037333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1358227353045148</v>
+        <v>0.1372883069008439</v>
       </c>
       <c r="T47">
-        <v>1.707698023267916</v>
+        <v>1.73549937488807</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.366488995944909</v>
+        <v>2.315043582989585</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1020300857264557</v>
+        <v>0.1020696670354283</v>
       </c>
       <c r="C48">
-        <v>304.9514679359939</v>
+        <v>297.9747366794427</v>
       </c>
       <c r="D48">
-        <v>558.3154679359939</v>
+        <v>557.9227366794428</v>
       </c>
       <c r="E48">
-        <v>108.464</v>
+        <v>115.048</v>
       </c>
       <c r="F48">
-        <v>302.864</v>
+        <v>309.448</v>
       </c>
       <c r="G48">
         <v>49.5</v>
@@ -5223,28 +5223,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M48">
-        <v>22.9570912</v>
+        <v>23.4561584</v>
       </c>
       <c r="N48">
-        <v>30.18957546666666</v>
+        <v>29.69050826666666</v>
       </c>
       <c r="O48">
-        <v>6.037915093333332</v>
+        <v>5.938101653333332</v>
       </c>
       <c r="P48">
-        <v>24.15166037333333</v>
+        <v>23.75240661333333</v>
       </c>
       <c r="Q48">
-        <v>28.07166037333333</v>
+        <v>27.67240661333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1372883069008439</v>
+        <v>0.1388091830857137</v>
       </c>
       <c r="T48">
-        <v>1.73549937488807</v>
+        <v>1.76434983411653</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.315043582989585</v>
+        <v>2.265787336542997</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1020696670354283</v>
+        <v>0.1021092483444008</v>
       </c>
       <c r="C49">
-        <v>297.9747366794427</v>
+        <v>290.9985575459501</v>
       </c>
       <c r="D49">
-        <v>557.9227366794428</v>
+        <v>557.5305575459502</v>
       </c>
       <c r="E49">
-        <v>115.048</v>
+        <v>121.632</v>
       </c>
       <c r="F49">
-        <v>309.448</v>
+        <v>316.032</v>
       </c>
       <c r="G49">
         <v>49.5</v>
@@ -5305,28 +5305,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M49">
-        <v>23.4561584</v>
+        <v>23.95522560000001</v>
       </c>
       <c r="N49">
-        <v>29.69050826666666</v>
+        <v>29.19144106666666</v>
       </c>
       <c r="O49">
-        <v>5.938101653333332</v>
+        <v>5.838288213333332</v>
       </c>
       <c r="P49">
-        <v>23.75240661333333</v>
+        <v>23.35315285333332</v>
       </c>
       <c r="Q49">
-        <v>27.67240661333333</v>
+        <v>27.27315285333332</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1388091830857137</v>
+        <v>0.1403885545084631</v>
       </c>
       <c r="T49">
-        <v>1.76434983411653</v>
+        <v>1.79430992639224</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.265787336542997</v>
+        <v>2.218583433698352</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1021092483444008</v>
+        <v>0.1021488296533734</v>
       </c>
       <c r="C50">
-        <v>290.9985575459503</v>
+        <v>284.0229293720269</v>
       </c>
       <c r="D50">
-        <v>557.5305575459503</v>
+        <v>557.1389293720268</v>
       </c>
       <c r="E50">
-        <v>121.632</v>
+        <v>128.216</v>
       </c>
       <c r="F50">
-        <v>316.032</v>
+        <v>322.616</v>
       </c>
       <c r="G50">
         <v>49.5</v>
@@ -5387,28 +5387,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M50">
-        <v>23.9552256</v>
+        <v>24.4542928</v>
       </c>
       <c r="N50">
-        <v>29.19144106666666</v>
+        <v>28.69237386666666</v>
       </c>
       <c r="O50">
-        <v>5.838288213333332</v>
+        <v>5.738474773333333</v>
       </c>
       <c r="P50">
-        <v>23.35315285333333</v>
+        <v>22.95389909333333</v>
       </c>
       <c r="Q50">
-        <v>27.27315285333333</v>
+        <v>26.87389909333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1403885545084631</v>
+        <v>0.142029862065438</v>
       </c>
       <c r="T50">
-        <v>1.79430992639224</v>
+        <v>1.825444924247389</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.218583433698352</v>
+        <v>2.173306220765732</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1021488296533734</v>
+        <v>0.1021884109623459</v>
       </c>
       <c r="C51">
-        <v>284.0229293720269</v>
+        <v>277.0478509974501</v>
       </c>
       <c r="D51">
-        <v>557.1389293720268</v>
+        <v>556.7478509974501</v>
       </c>
       <c r="E51">
-        <v>128.216</v>
+        <v>134.8</v>
       </c>
       <c r="F51">
-        <v>322.616</v>
+        <v>329.2</v>
       </c>
       <c r="G51">
         <v>49.5</v>
@@ -5469,28 +5469,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M51">
-        <v>24.4542928</v>
+        <v>24.95336</v>
       </c>
       <c r="N51">
-        <v>28.69237386666666</v>
+        <v>28.19330666666666</v>
       </c>
       <c r="O51">
-        <v>5.738474773333333</v>
+        <v>5.638661333333332</v>
       </c>
       <c r="P51">
-        <v>22.95389909333333</v>
+        <v>22.55464533333333</v>
       </c>
       <c r="Q51">
-        <v>26.87389909333333</v>
+        <v>26.47464533333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.142029862065438</v>
+        <v>0.1437368219246919</v>
       </c>
       <c r="T51">
-        <v>1.825444924247389</v>
+        <v>1.857825322016744</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.173306220765732</v>
+        <v>2.129840096350418</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1021884109623459</v>
+        <v>0.1022279922713185</v>
       </c>
       <c r="C52">
-        <v>277.0478509974501</v>
+        <v>270.0733212652527</v>
       </c>
       <c r="D52">
-        <v>556.7478509974501</v>
+        <v>556.3573212652527</v>
       </c>
       <c r="E52">
-        <v>134.8</v>
+        <v>141.384</v>
       </c>
       <c r="F52">
-        <v>329.2</v>
+        <v>335.784</v>
       </c>
       <c r="G52">
         <v>49.5</v>
@@ -5551,28 +5551,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M52">
-        <v>24.95336</v>
+        <v>25.4524272</v>
       </c>
       <c r="N52">
-        <v>28.19330666666666</v>
+        <v>27.69423946666666</v>
       </c>
       <c r="O52">
-        <v>5.638661333333332</v>
+        <v>5.538847893333332</v>
       </c>
       <c r="P52">
-        <v>22.55464533333333</v>
+        <v>22.15539157333333</v>
       </c>
       <c r="Q52">
-        <v>26.47464533333333</v>
+        <v>26.07539157333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1437368219246919</v>
+        <v>0.1455134536149358</v>
       </c>
       <c r="T52">
-        <v>1.857825322016744</v>
+        <v>1.891527368674644</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.129840096350418</v>
+        <v>2.088078525833743</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1022279922713185</v>
+        <v>0.1022675735802911</v>
       </c>
       <c r="C53">
-        <v>270.0733212652527</v>
+        <v>263.099339021712</v>
       </c>
       <c r="D53">
-        <v>556.3573212652527</v>
+        <v>555.967339021712</v>
       </c>
       <c r="E53">
-        <v>141.384</v>
+        <v>147.968</v>
       </c>
       <c r="F53">
-        <v>335.784</v>
+        <v>342.368</v>
       </c>
       <c r="G53">
         <v>49.5</v>
@@ -5633,28 +5633,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M53">
-        <v>25.4524272</v>
+        <v>25.9514944</v>
       </c>
       <c r="N53">
-        <v>27.69423946666666</v>
+        <v>27.19517226666666</v>
       </c>
       <c r="O53">
-        <v>5.538847893333332</v>
+        <v>5.439034453333332</v>
       </c>
       <c r="P53">
-        <v>22.15539157333333</v>
+        <v>21.75613781333333</v>
       </c>
       <c r="Q53">
-        <v>26.07539157333333</v>
+        <v>25.67613781333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1455134536149358</v>
+        <v>0.1473641116256064</v>
       </c>
       <c r="T53">
-        <v>1.891527368674644</v>
+        <v>1.926633667276623</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.088078525833743</v>
+        <v>2.047923169567709</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1022675735802911</v>
+        <v>0.1023071548892636</v>
       </c>
       <c r="C54">
-        <v>263.099339021712</v>
+        <v>256.1259031163369</v>
       </c>
       <c r="D54">
-        <v>555.967339021712</v>
+        <v>555.5779031163369</v>
       </c>
       <c r="E54">
-        <v>147.968</v>
+        <v>154.552</v>
       </c>
       <c r="F54">
-        <v>342.368</v>
+        <v>348.952</v>
       </c>
       <c r="G54">
         <v>49.5</v>
@@ -5715,28 +5715,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M54">
-        <v>25.9514944</v>
+        <v>26.4505616</v>
       </c>
       <c r="N54">
-        <v>27.19517226666666</v>
+        <v>26.69610506666666</v>
       </c>
       <c r="O54">
-        <v>5.439034453333332</v>
+        <v>5.339221013333333</v>
       </c>
       <c r="P54">
-        <v>21.75613781333333</v>
+        <v>21.35688405333333</v>
       </c>
       <c r="Q54">
-        <v>25.67613781333333</v>
+        <v>25.27688405333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1473641116256064</v>
+        <v>0.1492935210409865</v>
       </c>
       <c r="T54">
-        <v>1.926633667276623</v>
+        <v>1.963233850925496</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.047923169567709</v>
+        <v>2.009283109764545</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1023071548892636</v>
+        <v>0.1084811361982362</v>
       </c>
       <c r="C55">
-        <v>256.1259031163369</v>
+        <v>194.8184600270116</v>
       </c>
       <c r="D55">
-        <v>555.5779031163369</v>
+        <v>500.8544600270115</v>
       </c>
       <c r="E55">
-        <v>154.552</v>
+        <v>161.136</v>
       </c>
       <c r="F55">
-        <v>348.952</v>
+        <v>355.536</v>
       </c>
       <c r="G55">
         <v>49.5</v>
@@ -5797,45 +5797,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M55">
-        <v>26.4505616</v>
+        <v>31.99824</v>
       </c>
       <c r="N55">
-        <v>26.69610506666666</v>
+        <v>21.14842666666666</v>
       </c>
       <c r="O55">
-        <v>5.339221013333333</v>
+        <v>4.229685333333332</v>
       </c>
       <c r="P55">
-        <v>21.35688405333333</v>
+        <v>16.91874133333333</v>
       </c>
       <c r="Q55">
-        <v>25.27688405333333</v>
+        <v>20.83874133333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1492935210409865</v>
+        <v>0.1513068178222526</v>
       </c>
       <c r="T55">
-        <v>1.963233850925496</v>
+        <v>2.001425346906927</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.009283109764545</v>
+        <v>1.660924684190964</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1084811361982362</v>
+        <v>0.1086343175072088</v>
       </c>
       <c r="C56">
-        <v>194.8184600270116</v>
+        <v>187.0134466566843</v>
       </c>
       <c r="D56">
-        <v>500.8544600270115</v>
+        <v>499.6334466566843</v>
       </c>
       <c r="E56">
-        <v>161.136</v>
+        <v>167.72</v>
       </c>
       <c r="F56">
-        <v>355.536</v>
+        <v>362.12</v>
       </c>
       <c r="G56">
         <v>49.5</v>
@@ -5879,28 +5879,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M56">
-        <v>31.99824</v>
+        <v>32.5908</v>
       </c>
       <c r="N56">
-        <v>21.14842666666666</v>
+        <v>20.55586666666666</v>
       </c>
       <c r="O56">
-        <v>4.229685333333332</v>
+        <v>4.111173333333332</v>
       </c>
       <c r="P56">
-        <v>16.91874133333333</v>
+        <v>16.44469333333333</v>
       </c>
       <c r="Q56">
-        <v>20.83874133333333</v>
+        <v>20.36469333333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1513068178222526</v>
+        <v>0.153409594460464</v>
       </c>
       <c r="T56">
-        <v>2.001425346906927</v>
+        <v>2.041314242709756</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.660924684190964</v>
+        <v>1.63072605356931</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1086343175072088</v>
+        <v>0.1087874988161813</v>
       </c>
       <c r="C57">
-        <v>187.0134466566843</v>
+        <v>179.2143721291389</v>
       </c>
       <c r="D57">
-        <v>499.6334466566843</v>
+        <v>498.4183721291389</v>
       </c>
       <c r="E57">
-        <v>167.72</v>
+        <v>174.304</v>
       </c>
       <c r="F57">
-        <v>362.12</v>
+        <v>368.704</v>
       </c>
       <c r="G57">
         <v>49.5</v>
@@ -5961,28 +5961,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M57">
-        <v>32.5908</v>
+        <v>33.18336</v>
       </c>
       <c r="N57">
-        <v>20.55586666666666</v>
+        <v>19.96330666666666</v>
       </c>
       <c r="O57">
-        <v>4.111173333333332</v>
+        <v>3.992661333333333</v>
       </c>
       <c r="P57">
-        <v>16.44469333333333</v>
+        <v>15.97064533333333</v>
       </c>
       <c r="Q57">
-        <v>20.36469333333333</v>
+        <v>19.89064533333333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.153409594460464</v>
+        <v>0.1556079518549576</v>
       </c>
       <c r="T57">
-        <v>2.041314242709756</v>
+        <v>2.083016270139986</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.63072605356931</v>
+        <v>1.601605945469858</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1087874988161813</v>
+        <v>0.1089406801251539</v>
       </c>
       <c r="C58">
-        <v>179.2143721291389</v>
+        <v>171.4211932209075</v>
       </c>
       <c r="D58">
-        <v>498.4183721291389</v>
+        <v>497.2091932209075</v>
       </c>
       <c r="E58">
-        <v>174.304</v>
+        <v>180.888</v>
       </c>
       <c r="F58">
-        <v>368.704</v>
+        <v>375.288</v>
       </c>
       <c r="G58">
         <v>49.5</v>
@@ -6043,28 +6043,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M58">
-        <v>33.18336</v>
+        <v>33.77592</v>
       </c>
       <c r="N58">
-        <v>19.96330666666666</v>
+        <v>19.37074666666666</v>
       </c>
       <c r="O58">
-        <v>3.992661333333333</v>
+        <v>3.874149333333333</v>
       </c>
       <c r="P58">
-        <v>15.97064533333333</v>
+        <v>15.49659733333333</v>
       </c>
       <c r="Q58">
-        <v>19.89064533333333</v>
+        <v>19.41659733333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1556079518549576</v>
+        <v>0.1579085584305905</v>
       </c>
       <c r="T58">
-        <v>2.083016270139986</v>
+        <v>2.126657926753017</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.601605945469858</v>
+        <v>1.573507595549334</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1089406801251539</v>
+        <v>0.1090938614341265</v>
       </c>
       <c r="C59">
-        <v>171.4211932209075</v>
+        <v>163.6338671269538</v>
       </c>
       <c r="D59">
-        <v>497.2091932209075</v>
+        <v>496.0058671269538</v>
       </c>
       <c r="E59">
-        <v>180.888</v>
+        <v>187.472</v>
       </c>
       <c r="F59">
-        <v>375.288</v>
+        <v>381.872</v>
       </c>
       <c r="G59">
         <v>49.5</v>
@@ -6125,28 +6125,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M59">
-        <v>33.77592</v>
+        <v>34.36848</v>
       </c>
       <c r="N59">
-        <v>19.37074666666666</v>
+        <v>18.77818666666666</v>
       </c>
       <c r="O59">
-        <v>3.874149333333333</v>
+        <v>3.755637333333333</v>
       </c>
       <c r="P59">
-        <v>15.49659733333333</v>
+        <v>15.02254933333333</v>
       </c>
       <c r="Q59">
-        <v>19.41659733333333</v>
+        <v>18.94254933333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1579085584305905</v>
+        <v>0.1603187177003011</v>
       </c>
       <c r="T59">
-        <v>2.126657926753017</v>
+        <v>2.172377757490479</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.573507595549334</v>
+        <v>1.546378154246759</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1090938614341264</v>
+        <v>0.109247042743099</v>
       </c>
       <c r="C60">
-        <v>163.6338671269541</v>
+        <v>155.8523514556211</v>
       </c>
       <c r="D60">
-        <v>496.0058671269541</v>
+        <v>494.808351455621</v>
       </c>
       <c r="E60">
-        <v>187.472</v>
+        <v>194.056</v>
       </c>
       <c r="F60">
-        <v>381.872</v>
+        <v>388.456</v>
       </c>
       <c r="G60">
         <v>49.5</v>
@@ -6207,28 +6207,28 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M60">
-        <v>34.36848</v>
+        <v>34.96104</v>
       </c>
       <c r="N60">
-        <v>18.77818666666666</v>
+        <v>18.18562666666666</v>
       </c>
       <c r="O60">
-        <v>3.755637333333333</v>
+        <v>3.637125333333333</v>
       </c>
       <c r="P60">
-        <v>15.02254933333333</v>
+        <v>14.54850133333333</v>
       </c>
       <c r="Q60">
-        <v>18.94254933333333</v>
+        <v>18.46850133333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1603187177003011</v>
+        <v>0.1628464457148757</v>
       </c>
       <c r="T60">
-        <v>2.172377757490478</v>
+        <v>2.22032782387367</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.546378154246759</v>
+        <v>1.520168355022238</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.109247042743099</v>
+        <v>0.1386815424666237</v>
       </c>
       <c r="C61">
-        <v>155.8523514556211</v>
+        <v>-7.53822062894352</v>
       </c>
       <c r="D61">
-        <v>494.808351455621</v>
+        <v>338.0017793710564</v>
       </c>
       <c r="E61">
-        <v>194.056</v>
+        <v>200.64</v>
       </c>
       <c r="F61">
-        <v>388.456</v>
+        <v>395.04</v>
       </c>
       <c r="G61">
         <v>49.5</v>
@@ -6289,45 +6289,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M61">
-        <v>34.96104</v>
+        <v>57.991872</v>
       </c>
       <c r="N61">
-        <v>18.18562666666666</v>
+        <v>-4.84520533333334</v>
       </c>
       <c r="O61">
-        <v>3.637125333333333</v>
+        <v>-0.969041066666668</v>
       </c>
       <c r="P61">
-        <v>14.54850133333333</v>
+        <v>-3.876164266666672</v>
       </c>
       <c r="Q61">
-        <v>18.46850133333333</v>
+        <v>0.04383573333332835</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1628464457148757</v>
+        <v>0.1668643259923997</v>
       </c>
       <c r="T61">
-        <v>2.22032782387367</v>
+        <v>2.296545528039683</v>
       </c>
       <c r="U61">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2</v>
+        <v>0.1832900537049974</v>
       </c>
       <c r="W61">
-        <v>0.07199999999999999</v>
+        <v>0.1198930201161064</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.520168355022238</v>
+        <v>0.9164502685249868</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1386815424666237</v>
+        <v>0.1396915424666237</v>
       </c>
       <c r="C62">
-        <v>-7.53822062894352</v>
+        <v>-17.75813700859095</v>
       </c>
       <c r="D62">
-        <v>338.0017793710564</v>
+        <v>334.365862991409</v>
       </c>
       <c r="E62">
-        <v>200.64</v>
+        <v>207.224</v>
       </c>
       <c r="F62">
-        <v>395.04</v>
+        <v>401.624</v>
       </c>
       <c r="G62">
         <v>49.5</v>
@@ -6371,37 +6371,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M62">
-        <v>57.991872</v>
+        <v>58.9584032</v>
       </c>
       <c r="N62">
-        <v>-4.84520533333334</v>
+        <v>-5.811736533333338</v>
       </c>
       <c r="O62">
-        <v>-0.969041066666668</v>
+        <v>-1.162347306666668</v>
       </c>
       <c r="P62">
-        <v>-3.876164266666672</v>
+        <v>-4.649389226666671</v>
       </c>
       <c r="Q62">
-        <v>0.04383573333332835</v>
+        <v>-0.7293892266666706</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1668643259923997</v>
+        <v>0.1699685394793843</v>
       </c>
       <c r="T62">
-        <v>2.296545528039683</v>
+        <v>2.355431310809932</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1832900537049974</v>
+        <v>0.1802852987262269</v>
       </c>
       <c r="W62">
-        <v>0.1198930201161064</v>
+        <v>0.1203341181469899</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9164502685249868</v>
+        <v>0.9014264936311345</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1396915424666237</v>
+        <v>0.1407015424666237</v>
       </c>
       <c r="C63">
-        <v>-17.75813700859095</v>
+        <v>-27.90066211623184</v>
       </c>
       <c r="D63">
-        <v>334.365862991409</v>
+        <v>330.8073378837681</v>
       </c>
       <c r="E63">
-        <v>207.224</v>
+        <v>213.808</v>
       </c>
       <c r="F63">
-        <v>401.624</v>
+        <v>408.208</v>
       </c>
       <c r="G63">
         <v>49.5</v>
@@ -6453,37 +6453,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M63">
-        <v>58.9584032</v>
+        <v>59.9249344</v>
       </c>
       <c r="N63">
-        <v>-5.811736533333338</v>
+        <v>-6.778267733333337</v>
       </c>
       <c r="O63">
-        <v>-1.162347306666668</v>
+        <v>-1.355653546666667</v>
       </c>
       <c r="P63">
-        <v>-4.649389226666671</v>
+        <v>-5.422614186666669</v>
       </c>
       <c r="Q63">
-        <v>-0.7293892266666706</v>
+        <v>-1.502614186666669</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1699685394793843</v>
+        <v>0.1732361326235786</v>
       </c>
       <c r="T63">
-        <v>2.355431310809932</v>
+        <v>2.41741634530493</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1802852987262269</v>
+        <v>0.1773774713274168</v>
       </c>
       <c r="W63">
-        <v>0.1203341181469899</v>
+        <v>0.1207609872091352</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9014264936311345</v>
+        <v>0.886887356637084</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1407015424666237</v>
+        <v>0.1417115424666237</v>
       </c>
       <c r="C64">
-        <v>-27.90066211623184</v>
+        <v>-37.96824086671307</v>
       </c>
       <c r="D64">
-        <v>330.8073378837681</v>
+        <v>327.3237591332869</v>
       </c>
       <c r="E64">
-        <v>213.808</v>
+        <v>220.392</v>
       </c>
       <c r="F64">
-        <v>408.208</v>
+        <v>414.792</v>
       </c>
       <c r="G64">
         <v>49.5</v>
@@ -6535,37 +6535,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M64">
-        <v>59.9249344</v>
+        <v>60.8914656</v>
       </c>
       <c r="N64">
-        <v>-6.778267733333337</v>
+        <v>-7.744798933333342</v>
       </c>
       <c r="O64">
-        <v>-1.355653546666667</v>
+        <v>-1.548959786666669</v>
       </c>
       <c r="P64">
-        <v>-5.422614186666669</v>
+        <v>-6.195839146666674</v>
       </c>
       <c r="Q64">
-        <v>-1.502614186666669</v>
+        <v>-2.275839146666674</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1732361326235786</v>
+        <v>0.1766803524242159</v>
       </c>
       <c r="T64">
-        <v>2.41741634530493</v>
+        <v>2.482751922205063</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1773774713274168</v>
+        <v>0.1745619559095213</v>
       </c>
       <c r="W64">
-        <v>0.1207609872091352</v>
+        <v>0.1211743048724823</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.886887356637084</v>
+        <v>0.8728097795476064</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1417115424666237</v>
+        <v>0.1427215424666237</v>
       </c>
       <c r="C65">
-        <v>-37.96824086671307</v>
+        <v>-47.96321626300818</v>
       </c>
       <c r="D65">
-        <v>327.3237591332869</v>
+        <v>323.9127837369918</v>
       </c>
       <c r="E65">
-        <v>220.392</v>
+        <v>226.976</v>
       </c>
       <c r="F65">
-        <v>414.792</v>
+        <v>421.376</v>
       </c>
       <c r="G65">
         <v>49.5</v>
@@ -6617,37 +6617,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M65">
-        <v>60.8914656</v>
+        <v>61.8579968</v>
       </c>
       <c r="N65">
-        <v>-7.744798933333342</v>
+        <v>-8.711330133333341</v>
       </c>
       <c r="O65">
-        <v>-1.548959786666669</v>
+        <v>-1.742266026666668</v>
       </c>
       <c r="P65">
-        <v>-6.195839146666674</v>
+        <v>-6.969064106666673</v>
       </c>
       <c r="Q65">
-        <v>-2.275839146666674</v>
+        <v>-3.049064106666673</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1766803524242159</v>
+        <v>0.180315917769333</v>
       </c>
       <c r="T65">
-        <v>2.482751922205063</v>
+        <v>2.551717253377427</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1745619559095213</v>
+        <v>0.171834425348435</v>
       </c>
       <c r="W65">
-        <v>0.1211743048724823</v>
+        <v>0.1215747063588498</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8728097795476064</v>
+        <v>0.859172126742175</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1427215424666237</v>
+        <v>0.1437315424666237</v>
       </c>
       <c r="C66">
-        <v>-47.96321626300818</v>
+        <v>-57.88783465146923</v>
       </c>
       <c r="D66">
-        <v>323.9127837369918</v>
+        <v>320.5721653485307</v>
       </c>
       <c r="E66">
-        <v>226.976</v>
+        <v>233.56</v>
       </c>
       <c r="F66">
-        <v>421.376</v>
+        <v>427.96</v>
       </c>
       <c r="G66">
         <v>49.5</v>
@@ -6699,37 +6699,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M66">
-        <v>61.8579968</v>
+        <v>62.824528</v>
       </c>
       <c r="N66">
-        <v>-8.711330133333341</v>
+        <v>-9.67786133333334</v>
       </c>
       <c r="O66">
-        <v>-1.742266026666668</v>
+        <v>-1.935572266666668</v>
       </c>
       <c r="P66">
-        <v>-6.969064106666673</v>
+        <v>-7.742289066666672</v>
       </c>
       <c r="Q66">
-        <v>-3.049064106666673</v>
+        <v>-3.822289066666672</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.180315917769333</v>
+        <v>0.1841592297055997</v>
       </c>
       <c r="T66">
-        <v>2.551717253377427</v>
+        <v>2.624623460616782</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.171834425348435</v>
+        <v>0.169190818804613</v>
       </c>
       <c r="W66">
-        <v>0.1215747063588498</v>
+        <v>0.1219627877994828</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.859172126742175</v>
+        <v>0.8459540940230648</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1437315424666237</v>
+        <v>0.1447415424666237</v>
       </c>
       <c r="C67">
-        <v>-57.88783465146923</v>
+        <v>-67.74425065520433</v>
       </c>
       <c r="D67">
-        <v>320.5721653485307</v>
+        <v>317.2997493447957</v>
       </c>
       <c r="E67">
-        <v>233.56</v>
+        <v>240.144</v>
       </c>
       <c r="F67">
-        <v>427.96</v>
+        <v>434.544</v>
       </c>
       <c r="G67">
         <v>49.5</v>
@@ -6781,37 +6781,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M67">
-        <v>62.824528</v>
+        <v>63.79105920000001</v>
       </c>
       <c r="N67">
-        <v>-9.67786133333334</v>
+        <v>-10.64439253333335</v>
       </c>
       <c r="O67">
-        <v>-1.935572266666668</v>
+        <v>-2.128878506666669</v>
       </c>
       <c r="P67">
-        <v>-7.742289066666672</v>
+        <v>-8.515514026666676</v>
       </c>
       <c r="Q67">
-        <v>-3.822289066666672</v>
+        <v>-4.595514026666676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1841592297055997</v>
+        <v>0.1882286188145879</v>
       </c>
       <c r="T67">
-        <v>2.624623460616782</v>
+        <v>2.70181826828198</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.169190818804613</v>
+        <v>0.1666273215499976</v>
       </c>
       <c r="W67">
-        <v>0.1219627877994828</v>
+        <v>0.1223391091964604</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8459540940230648</v>
+        <v>0.8331366077499879</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1447415424666237</v>
+        <v>0.1457515424666238</v>
       </c>
       <c r="C68">
-        <v>-67.74425065520433</v>
+        <v>-77.53453180834686</v>
       </c>
       <c r="D68">
-        <v>317.2997493447957</v>
+        <v>314.0934681916531</v>
       </c>
       <c r="E68">
-        <v>240.144</v>
+        <v>246.728</v>
       </c>
       <c r="F68">
-        <v>434.544</v>
+        <v>441.128</v>
       </c>
       <c r="G68">
         <v>49.5</v>
@@ -6863,37 +6863,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M68">
-        <v>63.79105920000001</v>
+        <v>64.7575904</v>
       </c>
       <c r="N68">
-        <v>-10.64439253333335</v>
+        <v>-11.61092373333334</v>
       </c>
       <c r="O68">
-        <v>-2.128878506666669</v>
+        <v>-2.322184746666668</v>
       </c>
       <c r="P68">
-        <v>-8.515514026666676</v>
+        <v>-9.288738986666669</v>
       </c>
       <c r="Q68">
-        <v>-4.595514026666676</v>
+        <v>-5.368738986666669</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1882286188145879</v>
+        <v>0.1925446375665451</v>
       </c>
       <c r="T68">
-        <v>2.70181826828198</v>
+        <v>2.783691549139011</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1666273215499976</v>
+        <v>0.1641403466014902</v>
       </c>
       <c r="W68">
-        <v>0.1223391091964604</v>
+        <v>0.1227041971189013</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8331366077499879</v>
+        <v>0.8207017330074509</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1457515424666238</v>
+        <v>0.1467615424666237</v>
       </c>
       <c r="C69">
-        <v>-77.53453180834686</v>
+        <v>-87.26066291216222</v>
       </c>
       <c r="D69">
-        <v>314.0934681916531</v>
+        <v>310.9513370878378</v>
       </c>
       <c r="E69">
-        <v>246.728</v>
+        <v>253.312</v>
       </c>
       <c r="F69">
-        <v>441.128</v>
+        <v>447.712</v>
       </c>
       <c r="G69">
         <v>49.5</v>
@@ -6945,37 +6945,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M69">
-        <v>64.7575904</v>
+        <v>65.7241216</v>
       </c>
       <c r="N69">
-        <v>-11.61092373333334</v>
+        <v>-12.57745493333334</v>
       </c>
       <c r="O69">
-        <v>-2.322184746666668</v>
+        <v>-2.515490986666669</v>
       </c>
       <c r="P69">
-        <v>-9.288738986666669</v>
+        <v>-10.06196394666667</v>
       </c>
       <c r="Q69">
-        <v>-5.368738986666669</v>
+        <v>-6.141963946666674</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1925446375665451</v>
+        <v>0.1971304074904996</v>
       </c>
       <c r="T69">
-        <v>2.783691549139011</v>
+        <v>2.870681910049605</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1641403466014902</v>
+        <v>0.1617265179749977</v>
       </c>
       <c r="W69">
-        <v>0.1227041971189013</v>
+        <v>0.1230585471612703</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8207017330074509</v>
+        <v>0.8086325898749882</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1467615424666237</v>
+        <v>0.1866406819900546</v>
       </c>
       <c r="C70">
-        <v>-87.26066291216222</v>
+        <v>-181.8907557136649</v>
       </c>
       <c r="D70">
-        <v>310.9513370878378</v>
+        <v>222.9052442863351</v>
       </c>
       <c r="E70">
-        <v>253.312</v>
+        <v>259.8960000000001</v>
       </c>
       <c r="F70">
-        <v>447.712</v>
+        <v>454.296</v>
       </c>
       <c r="G70">
         <v>49.5</v>
@@ -7027,45 +7027,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M70">
-        <v>65.7241216</v>
+        <v>91.22263680000002</v>
       </c>
       <c r="N70">
-        <v>-12.57745493333334</v>
+        <v>-38.07597013333336</v>
       </c>
       <c r="O70">
-        <v>-2.515490986666669</v>
+        <v>-7.615194026666671</v>
       </c>
       <c r="P70">
-        <v>-10.06196394666667</v>
+        <v>-30.46077610666669</v>
       </c>
       <c r="Q70">
-        <v>-6.141963946666674</v>
+        <v>-26.54077610666668</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1971304074904996</v>
+        <v>0.2072028061948089</v>
       </c>
       <c r="T70">
-        <v>2.870681910049605</v>
+        <v>3.061751591488763</v>
       </c>
       <c r="U70">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1617265179749977</v>
+        <v>0.11652078591674</v>
       </c>
       <c r="W70">
-        <v>0.1230585471612703</v>
+        <v>0.1774026261879186</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8086325898749882</v>
+        <v>0.5826039295837001</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1866406819900546</v>
+        <v>0.1881906819900546</v>
       </c>
       <c r="C71">
-        <v>-181.8907557136649</v>
+        <v>-190.9012005049607</v>
       </c>
       <c r="D71">
-        <v>222.9052442863351</v>
+        <v>220.4787994950393</v>
       </c>
       <c r="E71">
-        <v>259.8960000000001</v>
+        <v>266.48</v>
       </c>
       <c r="F71">
-        <v>454.296</v>
+        <v>460.8800000000001</v>
       </c>
       <c r="G71">
         <v>49.5</v>
@@ -7109,37 +7109,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M71">
-        <v>91.22263680000002</v>
+        <v>92.54470400000001</v>
       </c>
       <c r="N71">
-        <v>-38.07597013333336</v>
+        <v>-39.39803733333335</v>
       </c>
       <c r="O71">
-        <v>-7.615194026666671</v>
+        <v>-7.87960746666667</v>
       </c>
       <c r="P71">
-        <v>-30.46077610666669</v>
+        <v>-31.51842986666668</v>
       </c>
       <c r="Q71">
-        <v>-26.54077610666668</v>
+        <v>-27.59842986666668</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2072028061948089</v>
+        <v>0.2125828997346359</v>
       </c>
       <c r="T71">
-        <v>3.061751591488763</v>
+        <v>3.163809977871723</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.11652078591674</v>
+        <v>0.1148562032607866</v>
       </c>
       <c r="W71">
-        <v>0.1774026261879186</v>
+        <v>0.1777368743852341</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5826039295837001</v>
+        <v>0.574281016303933</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1881906819900546</v>
+        <v>0.1897406819900546</v>
       </c>
       <c r="C72">
-        <v>-190.9012005049607</v>
+        <v>-199.8593878055386</v>
       </c>
       <c r="D72">
-        <v>220.4787994950393</v>
+        <v>218.1046121944614</v>
       </c>
       <c r="E72">
-        <v>266.48</v>
+        <v>273.0640000000001</v>
       </c>
       <c r="F72">
-        <v>460.8800000000001</v>
+        <v>467.4640000000001</v>
       </c>
       <c r="G72">
         <v>49.5</v>
@@ -7191,37 +7191,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M72">
-        <v>92.54470400000001</v>
+        <v>93.86677120000002</v>
       </c>
       <c r="N72">
-        <v>-39.39803733333335</v>
+        <v>-40.72010453333336</v>
       </c>
       <c r="O72">
-        <v>-7.87960746666667</v>
+        <v>-8.144020906666672</v>
       </c>
       <c r="P72">
-        <v>-31.51842986666668</v>
+        <v>-32.57608362666669</v>
       </c>
       <c r="Q72">
-        <v>-27.59842986666668</v>
+        <v>-28.65608362666669</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2125828997346359</v>
+        <v>0.2183340342082441</v>
       </c>
       <c r="T72">
-        <v>3.163809977871723</v>
+        <v>3.272906873660403</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1148562032607866</v>
+        <v>0.1132385102571136</v>
       </c>
       <c r="W72">
-        <v>0.1777368743852341</v>
+        <v>0.1780617071403716</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.574281016303933</v>
+        <v>0.5661925512855677</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1897406819900546</v>
+        <v>0.1912906819900546</v>
       </c>
       <c r="C73">
-        <v>-199.8593878055385</v>
+        <v>-208.7669878071147</v>
       </c>
       <c r="D73">
-        <v>218.1046121944614</v>
+        <v>215.7810121928852</v>
       </c>
       <c r="E73">
-        <v>273.064</v>
+        <v>279.6479999999999</v>
       </c>
       <c r="F73">
-        <v>467.4639999999999</v>
+        <v>474.0479999999999</v>
       </c>
       <c r="G73">
         <v>49.5</v>
@@ -7273,37 +7273,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M73">
-        <v>93.86677119999999</v>
+        <v>95.18883839999999</v>
       </c>
       <c r="N73">
-        <v>-40.72010453333333</v>
+        <v>-42.04217173333333</v>
       </c>
       <c r="O73">
-        <v>-8.144020906666666</v>
+        <v>-8.408434346666667</v>
       </c>
       <c r="P73">
-        <v>-32.57608362666666</v>
+        <v>-33.63373738666667</v>
       </c>
       <c r="Q73">
-        <v>-28.65608362666666</v>
+        <v>-29.71373738666666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.218334034208244</v>
+        <v>0.2244959640013956</v>
       </c>
       <c r="T73">
-        <v>3.272906873660402</v>
+        <v>3.389796404862559</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1132385102571136</v>
+        <v>0.1116657531702092</v>
       </c>
       <c r="W73">
-        <v>0.1780617071403716</v>
+        <v>0.178377516763422</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5661925512855679</v>
+        <v>0.5583287658510461</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1912906819900546</v>
+        <v>0.1928406819900546</v>
       </c>
       <c r="C74">
-        <v>-208.7669878071147</v>
+        <v>-217.625600277435</v>
       </c>
       <c r="D74">
-        <v>215.7810121928852</v>
+        <v>213.506399722565</v>
       </c>
       <c r="E74">
-        <v>279.6479999999999</v>
+        <v>286.232</v>
       </c>
       <c r="F74">
-        <v>474.0479999999999</v>
+        <v>480.6319999999999</v>
       </c>
       <c r="G74">
         <v>49.5</v>
@@ -7355,37 +7355,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M74">
-        <v>95.18883839999999</v>
+        <v>96.51090559999999</v>
       </c>
       <c r="N74">
-        <v>-42.04217173333333</v>
+        <v>-43.36423893333333</v>
       </c>
       <c r="O74">
-        <v>-8.408434346666667</v>
+        <v>-8.672847786666665</v>
       </c>
       <c r="P74">
-        <v>-33.63373738666667</v>
+        <v>-34.69139114666666</v>
       </c>
       <c r="Q74">
-        <v>-29.71373738666666</v>
+        <v>-30.77139114666666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2244959640013956</v>
+        <v>0.2311143330384843</v>
       </c>
       <c r="T74">
-        <v>3.389796404862559</v>
+        <v>3.515344419857468</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1116657531702092</v>
+        <v>0.1101360853185625</v>
       </c>
       <c r="W74">
-        <v>0.178377516763422</v>
+        <v>0.1786846740680327</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5583287658510461</v>
+        <v>0.5506804265928127</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1928406819900546</v>
+        <v>0.1943906819900546</v>
       </c>
       <c r="C75">
-        <v>-217.625600277435</v>
+        <v>-226.4367582333567</v>
       </c>
       <c r="D75">
-        <v>213.506399722565</v>
+        <v>211.2792417666433</v>
       </c>
       <c r="E75">
-        <v>286.232</v>
+        <v>292.8159999999999</v>
       </c>
       <c r="F75">
-        <v>480.6319999999999</v>
+        <v>487.216</v>
       </c>
       <c r="G75">
         <v>49.5</v>
@@ -7437,37 +7437,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M75">
-        <v>96.51090559999999</v>
+        <v>97.83297279999999</v>
       </c>
       <c r="N75">
-        <v>-43.36423893333333</v>
+        <v>-44.68630613333333</v>
       </c>
       <c r="O75">
-        <v>-8.672847786666665</v>
+        <v>-8.937261226666667</v>
       </c>
       <c r="P75">
-        <v>-34.69139114666666</v>
+        <v>-35.74904490666667</v>
       </c>
       <c r="Q75">
-        <v>-30.77139114666666</v>
+        <v>-31.82904490666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2311143330384843</v>
+        <v>0.2382418073861183</v>
       </c>
       <c r="T75">
-        <v>3.515344419857468</v>
+        <v>3.650549974467371</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1101360853185625</v>
+        <v>0.1086477598412847</v>
       </c>
       <c r="W75">
-        <v>0.1786846740680327</v>
+        <v>0.17898352982387</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5506804265928127</v>
+        <v>0.5432387992064232</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1943906819900546</v>
+        <v>0.1959406819900546</v>
       </c>
       <c r="C76">
-        <v>-226.4367582333567</v>
+        <v>-235.2019313864131</v>
       </c>
       <c r="D76">
-        <v>211.2792417666433</v>
+        <v>209.0980686135869</v>
       </c>
       <c r="E76">
-        <v>292.8159999999999</v>
+        <v>299.4</v>
       </c>
       <c r="F76">
-        <v>487.216</v>
+        <v>493.8</v>
       </c>
       <c r="G76">
         <v>49.5</v>
@@ -7519,37 +7519,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M76">
-        <v>97.83297279999999</v>
+        <v>99.15504</v>
       </c>
       <c r="N76">
-        <v>-44.68630613333333</v>
+        <v>-46.00837333333334</v>
       </c>
       <c r="O76">
-        <v>-8.937261226666667</v>
+        <v>-9.201674666666667</v>
       </c>
       <c r="P76">
-        <v>-35.74904490666667</v>
+        <v>-36.80669866666667</v>
       </c>
       <c r="Q76">
-        <v>-31.82904490666667</v>
+        <v>-32.88669866666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2382418073861183</v>
+        <v>0.2459394796815631</v>
       </c>
       <c r="T76">
-        <v>3.650549974467371</v>
+        <v>3.796571973446067</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1086477598412847</v>
+        <v>0.1071991230434008</v>
       </c>
       <c r="W76">
-        <v>0.17898352982387</v>
+        <v>0.1792744160928851</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5432387992064232</v>
+        <v>0.5359956152170042</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1959406819900546</v>
+        <v>0.1974906819900546</v>
       </c>
       <c r="C77">
-        <v>-235.2019313864131</v>
+        <v>-243.9225293771343</v>
       </c>
       <c r="D77">
-        <v>209.0980686135869</v>
+        <v>206.9614706228658</v>
       </c>
       <c r="E77">
-        <v>299.4</v>
+        <v>305.984</v>
       </c>
       <c r="F77">
-        <v>493.8</v>
+        <v>500.384</v>
       </c>
       <c r="G77">
         <v>49.5</v>
@@ -7601,37 +7601,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M77">
-        <v>99.15504</v>
+        <v>100.4771072</v>
       </c>
       <c r="N77">
-        <v>-46.00837333333334</v>
+        <v>-47.33044053333334</v>
       </c>
       <c r="O77">
-        <v>-9.201674666666667</v>
+        <v>-9.466088106666669</v>
       </c>
       <c r="P77">
-        <v>-36.80669866666667</v>
+        <v>-37.86435242666668</v>
       </c>
       <c r="Q77">
-        <v>-32.88669866666667</v>
+        <v>-33.94435242666668</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2459394796815631</v>
+        <v>0.2542786246682949</v>
       </c>
       <c r="T77">
-        <v>3.796571973446067</v>
+        <v>3.954762472339653</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1071991230434008</v>
+        <v>0.105788608266514</v>
       </c>
       <c r="W77">
-        <v>0.1792744160928851</v>
+        <v>0.179557647460084</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5359956152170042</v>
+        <v>0.52894304133257</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1974906819900546</v>
+        <v>0.1990406819900546</v>
       </c>
       <c r="C78">
-        <v>-243.9225293771343</v>
+        <v>-252.5999048130793</v>
       </c>
       <c r="D78">
-        <v>206.9614706228658</v>
+        <v>204.8680951869208</v>
       </c>
       <c r="E78">
-        <v>305.984</v>
+        <v>312.568</v>
       </c>
       <c r="F78">
-        <v>500.384</v>
+        <v>506.968</v>
       </c>
       <c r="G78">
         <v>49.5</v>
@@ -7683,37 +7683,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M78">
-        <v>100.4771072</v>
+        <v>101.7991744</v>
       </c>
       <c r="N78">
-        <v>-47.33044053333334</v>
+        <v>-48.65250773333335</v>
       </c>
       <c r="O78">
-        <v>-9.466088106666669</v>
+        <v>-9.730501546666671</v>
       </c>
       <c r="P78">
-        <v>-37.86435242666668</v>
+        <v>-38.92200618666668</v>
       </c>
       <c r="Q78">
-        <v>-33.94435242666668</v>
+        <v>-35.00200618666668</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2542786246682949</v>
+        <v>0.2633429126973512</v>
       </c>
       <c r="T78">
-        <v>3.954762472339653</v>
+        <v>4.126708666789203</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.105788608266514</v>
+        <v>0.1044147302370787</v>
       </c>
       <c r="W78">
-        <v>0.179557647460084</v>
+        <v>0.1798335221683946</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.52894304133257</v>
+        <v>0.5220736511853936</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1990406819900546</v>
+        <v>0.2005906819900546</v>
       </c>
       <c r="C79">
-        <v>-252.5999048130793</v>
+        <v>-261.2353561243418</v>
       </c>
       <c r="D79">
-        <v>204.8680951869208</v>
+        <v>202.8166438756582</v>
       </c>
       <c r="E79">
-        <v>312.568</v>
+        <v>319.152</v>
       </c>
       <c r="F79">
-        <v>506.968</v>
+        <v>513.552</v>
       </c>
       <c r="G79">
         <v>49.5</v>
@@ -7765,37 +7765,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M79">
-        <v>101.7991744</v>
+        <v>103.1212416</v>
       </c>
       <c r="N79">
-        <v>-48.65250773333335</v>
+        <v>-49.97457493333334</v>
       </c>
       <c r="O79">
-        <v>-9.730501546666671</v>
+        <v>-9.99491498666667</v>
       </c>
       <c r="P79">
-        <v>-38.92200618666668</v>
+        <v>-39.97965994666667</v>
       </c>
       <c r="Q79">
-        <v>-35.00200618666668</v>
+        <v>-36.05965994666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2633429126973512</v>
+        <v>0.2732312269108671</v>
       </c>
       <c r="T79">
-        <v>4.126708666789203</v>
+        <v>4.314286333461439</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1044147302370787</v>
+        <v>0.1030760798494239</v>
       </c>
       <c r="W79">
-        <v>0.1798335221683946</v>
+        <v>0.1801023231662357</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5220736511853936</v>
+        <v>0.5153803992471194</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2005906819900546</v>
+        <v>0.2021406819900546</v>
       </c>
       <c r="C80">
-        <v>-261.2353561243418</v>
+        <v>-269.8301302491935</v>
       </c>
       <c r="D80">
-        <v>202.8166438756582</v>
+        <v>200.8058697508065</v>
       </c>
       <c r="E80">
-        <v>319.152</v>
+        <v>325.736</v>
       </c>
       <c r="F80">
-        <v>513.552</v>
+        <v>520.136</v>
       </c>
       <c r="G80">
         <v>49.5</v>
@@ -7847,37 +7847,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M80">
-        <v>103.1212416</v>
+        <v>104.4433088</v>
       </c>
       <c r="N80">
-        <v>-49.97457493333334</v>
+        <v>-51.29664213333334</v>
       </c>
       <c r="O80">
-        <v>-9.99491498666667</v>
+        <v>-10.25932842666667</v>
       </c>
       <c r="P80">
-        <v>-39.97965994666667</v>
+        <v>-41.03731370666667</v>
       </c>
       <c r="Q80">
-        <v>-36.05965994666667</v>
+        <v>-37.11731370666666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2732312269108671</v>
+        <v>0.2840612853351941</v>
       </c>
       <c r="T80">
-        <v>4.314286333461439</v>
+        <v>4.519728539816746</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1030760798494239</v>
+        <v>0.1017713193450008</v>
       </c>
       <c r="W80">
-        <v>0.1801023231662357</v>
+        <v>0.1803643190755238</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5153803992471194</v>
+        <v>0.5088565967250041</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2021406819900546</v>
+        <v>0.2036906819900546</v>
       </c>
       <c r="C81">
-        <v>-269.8301302491935</v>
+        <v>-278.385425161539</v>
       </c>
       <c r="D81">
-        <v>200.8058697508065</v>
+        <v>198.834574838461</v>
       </c>
       <c r="E81">
-        <v>325.736</v>
+        <v>332.3200000000001</v>
       </c>
       <c r="F81">
-        <v>520.136</v>
+        <v>526.72</v>
       </c>
       <c r="G81">
         <v>49.5</v>
@@ -7929,37 +7929,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M81">
-        <v>104.4433088</v>
+        <v>105.765376</v>
       </c>
       <c r="N81">
-        <v>-51.29664213333334</v>
+        <v>-52.61870933333334</v>
       </c>
       <c r="O81">
-        <v>-10.25932842666667</v>
+        <v>-10.52374186666667</v>
       </c>
       <c r="P81">
-        <v>-41.03731370666667</v>
+        <v>-42.09496746666667</v>
       </c>
       <c r="Q81">
-        <v>-37.11731370666666</v>
+        <v>-38.17496746666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2840612853351941</v>
+        <v>0.2959743496019539</v>
       </c>
       <c r="T81">
-        <v>4.519728539816746</v>
+        <v>4.745714966807584</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1017713193450008</v>
+        <v>0.1004991778531883</v>
       </c>
       <c r="W81">
-        <v>0.1803643190755238</v>
+        <v>0.1806197650870798</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5088565967250041</v>
+        <v>0.5024958892659415</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2036906819900546</v>
+        <v>0.234239989224009</v>
       </c>
       <c r="C82">
-        <v>-278.385425161539</v>
+        <v>-317.2038704111194</v>
       </c>
       <c r="D82">
-        <v>198.834574838461</v>
+        <v>166.6001295888805</v>
       </c>
       <c r="E82">
-        <v>332.3200000000001</v>
+        <v>338.904</v>
       </c>
       <c r="F82">
-        <v>526.72</v>
+        <v>533.304</v>
       </c>
       <c r="G82">
         <v>49.5</v>
@@ -8011,45 +8011,45 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M82">
-        <v>105.765376</v>
+        <v>125.7530832</v>
       </c>
       <c r="N82">
-        <v>-52.61870933333334</v>
+        <v>-72.60641653333333</v>
       </c>
       <c r="O82">
-        <v>-10.52374186666667</v>
+        <v>-14.52128330666667</v>
       </c>
       <c r="P82">
-        <v>-42.09496746666667</v>
+        <v>-58.08513322666666</v>
       </c>
       <c r="Q82">
-        <v>-38.17496746666667</v>
+        <v>-54.16513322666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2959743496019539</v>
+        <v>0.3125588271281324</v>
       </c>
       <c r="T82">
-        <v>4.745714966807584</v>
+        <v>5.060316377135603</v>
       </c>
       <c r="U82">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1004991778531883</v>
+        <v>0.08452542922091419</v>
       </c>
       <c r="W82">
-        <v>0.1806197650870798</v>
+        <v>0.2158689037897084</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.5024958892659415</v>
+        <v>0.422627146104571</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.234239989224009</v>
+        <v>0.236139989224009</v>
       </c>
       <c r="C83">
-        <v>-317.2038704111194</v>
+        <v>-325.4508958610492</v>
       </c>
       <c r="D83">
-        <v>166.6001295888805</v>
+        <v>164.9371041389508</v>
       </c>
       <c r="E83">
-        <v>338.904</v>
+        <v>345.4880000000001</v>
       </c>
       <c r="F83">
-        <v>533.304</v>
+        <v>539.888</v>
       </c>
       <c r="G83">
         <v>49.5</v>
@@ -8093,37 +8093,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M83">
-        <v>125.7530832</v>
+        <v>127.3055904</v>
       </c>
       <c r="N83">
-        <v>-72.60641653333333</v>
+        <v>-74.15892373333335</v>
       </c>
       <c r="O83">
-        <v>-14.52128330666667</v>
+        <v>-14.83178474666667</v>
       </c>
       <c r="P83">
-        <v>-58.08513322666666</v>
+        <v>-59.32713898666668</v>
       </c>
       <c r="Q83">
-        <v>-54.16513322666666</v>
+        <v>-55.40713898666668</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3125588271281324</v>
+        <v>0.3273787619685843</v>
       </c>
       <c r="T83">
-        <v>5.060316377135603</v>
+        <v>5.341445064754248</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08452542922091419</v>
+        <v>0.08349463130358596</v>
       </c>
       <c r="W83">
-        <v>0.2158689037897084</v>
+        <v>0.2161119659386145</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.422627146104571</v>
+        <v>0.4174731565179297</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.236139989224009</v>
+        <v>0.238039989224009</v>
       </c>
       <c r="C84">
-        <v>-325.4508958610492</v>
+        <v>-333.6650483549656</v>
       </c>
       <c r="D84">
-        <v>164.9371041389508</v>
+        <v>163.3069516450343</v>
       </c>
       <c r="E84">
-        <v>345.4880000000001</v>
+        <v>352.072</v>
       </c>
       <c r="F84">
-        <v>539.888</v>
+        <v>546.472</v>
       </c>
       <c r="G84">
         <v>49.5</v>
@@ -8175,37 +8175,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M84">
-        <v>127.3055904</v>
+        <v>128.8580976</v>
       </c>
       <c r="N84">
-        <v>-74.15892373333335</v>
+        <v>-75.71143093333335</v>
       </c>
       <c r="O84">
-        <v>-14.83178474666667</v>
+        <v>-15.14228618666667</v>
       </c>
       <c r="P84">
-        <v>-59.32713898666668</v>
+        <v>-60.56914474666668</v>
       </c>
       <c r="Q84">
-        <v>-55.40713898666668</v>
+        <v>-56.64914474666668</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3273787619685843</v>
+        <v>0.3439422185549716</v>
       </c>
       <c r="T84">
-        <v>5.341445064754248</v>
+        <v>5.655647715622146</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08349463130358596</v>
+        <v>0.08248867189028974</v>
       </c>
       <c r="W84">
-        <v>0.2161119659386145</v>
+        <v>0.2163491711682697</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4174731565179297</v>
+        <v>0.4124433594514487</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.238039989224009</v>
+        <v>0.239939989224009</v>
       </c>
       <c r="C85">
-        <v>-333.6650483549656</v>
+        <v>-341.8472930513097</v>
       </c>
       <c r="D85">
-        <v>163.3069516450343</v>
+        <v>161.7087069486903</v>
       </c>
       <c r="E85">
-        <v>352.072</v>
+        <v>358.6560000000001</v>
       </c>
       <c r="F85">
-        <v>546.472</v>
+        <v>553.056</v>
       </c>
       <c r="G85">
         <v>49.5</v>
@@ -8257,37 +8257,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M85">
-        <v>128.8580976</v>
+        <v>130.4106048</v>
       </c>
       <c r="N85">
-        <v>-75.71143093333335</v>
+        <v>-77.26393813333335</v>
       </c>
       <c r="O85">
-        <v>-15.14228618666667</v>
+        <v>-15.45278762666667</v>
       </c>
       <c r="P85">
-        <v>-60.56914474666668</v>
+        <v>-61.81115050666669</v>
       </c>
       <c r="Q85">
-        <v>-56.64914474666668</v>
+        <v>-57.89115050666668</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3439422185549716</v>
+        <v>0.3625761072146574</v>
       </c>
       <c r="T85">
-        <v>5.655647715622146</v>
+        <v>6.009125697848531</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08248867189028974</v>
+        <v>0.08150666389159582</v>
       </c>
       <c r="W85">
-        <v>0.2163491711682697</v>
+        <v>0.2165807286543617</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4124433594514487</v>
+        <v>0.407533319457979</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.239939989224009</v>
+        <v>0.241839989224009</v>
       </c>
       <c r="C86">
-        <v>-341.8472930513096</v>
+        <v>-349.9985576916451</v>
       </c>
       <c r="D86">
-        <v>161.7087069486903</v>
+        <v>160.1414423083549</v>
       </c>
       <c r="E86">
-        <v>358.6559999999999</v>
+        <v>365.24</v>
       </c>
       <c r="F86">
-        <v>553.0559999999999</v>
+        <v>559.64</v>
       </c>
       <c r="G86">
         <v>49.5</v>
@@ -8339,37 +8339,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M86">
-        <v>130.4106048</v>
+        <v>131.963112</v>
       </c>
       <c r="N86">
-        <v>-77.26393813333333</v>
+        <v>-78.81644533333333</v>
       </c>
       <c r="O86">
-        <v>-15.45278762666667</v>
+        <v>-15.76328906666667</v>
       </c>
       <c r="P86">
-        <v>-61.81115050666666</v>
+        <v>-63.05315626666667</v>
       </c>
       <c r="Q86">
-        <v>-57.89115050666666</v>
+        <v>-59.13315626666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3625761072146572</v>
+        <v>0.383694514362301</v>
       </c>
       <c r="T86">
-        <v>6.009125697848527</v>
+        <v>6.409734077705095</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08150666389159583</v>
+        <v>0.0805477619634594</v>
       </c>
       <c r="W86">
-        <v>0.2165807286543617</v>
+        <v>0.2168068377290163</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4075333194579791</v>
+        <v>0.402738809817297</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.241839989224009</v>
+        <v>0.243739989224009</v>
       </c>
       <c r="C87">
-        <v>-349.9985576916451</v>
+        <v>-358.119734396457</v>
       </c>
       <c r="D87">
-        <v>160.1414423083549</v>
+        <v>158.604265603543</v>
       </c>
       <c r="E87">
-        <v>365.24</v>
+        <v>371.824</v>
       </c>
       <c r="F87">
-        <v>559.64</v>
+        <v>566.2239999999999</v>
       </c>
       <c r="G87">
         <v>49.5</v>
@@ -8421,37 +8421,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M87">
-        <v>131.963112</v>
+        <v>133.5156192</v>
       </c>
       <c r="N87">
-        <v>-78.81644533333333</v>
+        <v>-80.36895253333334</v>
       </c>
       <c r="O87">
-        <v>-15.76328906666667</v>
+        <v>-16.07379050666667</v>
       </c>
       <c r="P87">
-        <v>-63.05315626666667</v>
+        <v>-64.29516202666667</v>
       </c>
       <c r="Q87">
-        <v>-59.13315626666667</v>
+        <v>-60.37516202666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.383694514362301</v>
+        <v>0.4078298368167511</v>
       </c>
       <c r="T87">
-        <v>6.409734077705095</v>
+        <v>6.867572226112602</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0805477619634594</v>
+        <v>0.07961116008016336</v>
       </c>
       <c r="W87">
-        <v>0.2168068377290163</v>
+        <v>0.2170276884530975</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.402738809817297</v>
+        <v>0.3980558004008168</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.243739989224009</v>
+        <v>0.245639989224009</v>
       </c>
       <c r="C88">
-        <v>-358.119734396457</v>
+        <v>-366.2116813585084</v>
       </c>
       <c r="D88">
-        <v>158.604265603543</v>
+        <v>157.0963186414916</v>
       </c>
       <c r="E88">
-        <v>371.824</v>
+        <v>378.408</v>
       </c>
       <c r="F88">
-        <v>566.2239999999999</v>
+        <v>572.808</v>
       </c>
       <c r="G88">
         <v>49.5</v>
@@ -8503,37 +8503,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M88">
-        <v>133.5156192</v>
+        <v>135.0681264</v>
       </c>
       <c r="N88">
-        <v>-80.36895253333334</v>
+        <v>-81.92145973333335</v>
       </c>
       <c r="O88">
-        <v>-16.07379050666667</v>
+        <v>-16.38429194666667</v>
       </c>
       <c r="P88">
-        <v>-64.29516202666667</v>
+        <v>-65.53716778666669</v>
       </c>
       <c r="Q88">
-        <v>-60.37516202666667</v>
+        <v>-61.61716778666668</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4078298368167511</v>
+        <v>0.4356782858026551</v>
       </c>
       <c r="T88">
-        <v>6.867572226112602</v>
+        <v>7.395847012736649</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07961116008016336</v>
+        <v>0.07869608927464423</v>
       </c>
       <c r="W88">
-        <v>0.2170276884530975</v>
+        <v>0.2172434621490389</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3980558004008168</v>
+        <v>0.3934804463732211</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.245639989224009</v>
+        <v>0.247539989224009</v>
       </c>
       <c r="C89">
-        <v>-366.2116813585084</v>
+        <v>-374.2752244405069</v>
       </c>
       <c r="D89">
-        <v>157.0963186414916</v>
+        <v>155.6167755594931</v>
       </c>
       <c r="E89">
-        <v>378.408</v>
+        <v>384.992</v>
       </c>
       <c r="F89">
-        <v>572.808</v>
+        <v>579.3919999999999</v>
       </c>
       <c r="G89">
         <v>49.5</v>
@@ -8585,37 +8585,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M89">
-        <v>135.0681264</v>
+        <v>136.6206336</v>
       </c>
       <c r="N89">
-        <v>-81.92145973333335</v>
+        <v>-83.47396693333333</v>
       </c>
       <c r="O89">
-        <v>-16.38429194666667</v>
+        <v>-16.69479338666667</v>
       </c>
       <c r="P89">
-        <v>-65.53716778666669</v>
+        <v>-66.77917354666667</v>
       </c>
       <c r="Q89">
-        <v>-61.61716778666668</v>
+        <v>-62.85917354666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4356782858026551</v>
+        <v>0.4681681429528763</v>
       </c>
       <c r="T89">
-        <v>7.395847012736649</v>
+        <v>8.01216759713137</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07869608927464423</v>
+        <v>0.07780181553288693</v>
       </c>
       <c r="W89">
-        <v>0.2172434621490389</v>
+        <v>0.2174543318973453</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3934804463732211</v>
+        <v>0.3890090776644346</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.247539989224009</v>
+        <v>0.249439989224009</v>
       </c>
       <c r="C90">
-        <v>-374.2752244405069</v>
+        <v>-382.3111586833329</v>
       </c>
       <c r="D90">
-        <v>155.6167755594931</v>
+        <v>154.1648413166671</v>
       </c>
       <c r="E90">
-        <v>384.992</v>
+        <v>391.576</v>
       </c>
       <c r="F90">
-        <v>579.3919999999999</v>
+        <v>585.976</v>
       </c>
       <c r="G90">
         <v>49.5</v>
@@ -8667,37 +8667,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M90">
-        <v>136.6206336</v>
+        <v>138.1731408</v>
       </c>
       <c r="N90">
-        <v>-83.47396693333333</v>
+        <v>-85.02647413333334</v>
       </c>
       <c r="O90">
-        <v>-16.69479338666667</v>
+        <v>-17.00529482666667</v>
       </c>
       <c r="P90">
-        <v>-66.77917354666667</v>
+        <v>-68.02117930666667</v>
       </c>
       <c r="Q90">
-        <v>-62.85917354666667</v>
+        <v>-64.10117930666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4681681429528763</v>
+        <v>0.5065652468576832</v>
       </c>
       <c r="T90">
-        <v>8.01216759713137</v>
+        <v>8.740546469597859</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07780181553288693</v>
+        <v>0.07692763783027022</v>
       </c>
       <c r="W90">
-        <v>0.2174543318973453</v>
+        <v>0.2176604629996223</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3890090776644346</v>
+        <v>0.3846381891513511</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.249439989224009</v>
+        <v>0.251339989224009</v>
       </c>
       <c r="C91">
-        <v>-382.3111586833329</v>
+        <v>-390.3202497306152</v>
       </c>
       <c r="D91">
-        <v>154.1648413166671</v>
+        <v>152.7397502693848</v>
       </c>
       <c r="E91">
-        <v>391.576</v>
+        <v>398.16</v>
       </c>
       <c r="F91">
-        <v>585.976</v>
+        <v>592.5599999999999</v>
       </c>
       <c r="G91">
         <v>49.5</v>
@@ -8749,37 +8749,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M91">
-        <v>138.1731408</v>
+        <v>139.725648</v>
       </c>
       <c r="N91">
-        <v>-85.02647413333334</v>
+        <v>-86.57898133333335</v>
       </c>
       <c r="O91">
-        <v>-17.00529482666667</v>
+        <v>-17.31579626666667</v>
       </c>
       <c r="P91">
-        <v>-68.02117930666667</v>
+        <v>-69.26318506666668</v>
       </c>
       <c r="Q91">
-        <v>-64.10117930666667</v>
+        <v>-65.34318506666668</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5065652468576832</v>
+        <v>0.5526417715434515</v>
       </c>
       <c r="T91">
-        <v>8.740546469597859</v>
+        <v>9.614601116557644</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07692763783027022</v>
+        <v>0.07607288629882276</v>
       </c>
       <c r="W91">
-        <v>0.2176604629996223</v>
+        <v>0.2178620134107376</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3846381891513511</v>
+        <v>0.3803644314941138</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.251339989224009</v>
+        <v>0.253239989224009</v>
       </c>
       <c r="C92">
-        <v>-390.3202497306152</v>
+        <v>-398.3032351750199</v>
       </c>
       <c r="D92">
-        <v>152.7397502693848</v>
+        <v>151.3407648249801</v>
       </c>
       <c r="E92">
-        <v>398.16</v>
+        <v>404.744</v>
       </c>
       <c r="F92">
-        <v>592.5599999999999</v>
+        <v>599.144</v>
       </c>
       <c r="G92">
         <v>49.5</v>
@@ -8831,37 +8831,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M92">
-        <v>139.725648</v>
+        <v>141.2781552</v>
       </c>
       <c r="N92">
-        <v>-86.57898133333335</v>
+        <v>-88.13148853333335</v>
       </c>
       <c r="O92">
-        <v>-17.31579626666667</v>
+        <v>-17.62629770666667</v>
       </c>
       <c r="P92">
-        <v>-69.26318506666668</v>
+        <v>-70.50519082666668</v>
       </c>
       <c r="Q92">
-        <v>-65.34318506666668</v>
+        <v>-66.58519082666668</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5526417715434515</v>
+        <v>0.6089575239371685</v>
       </c>
       <c r="T92">
-        <v>9.614601116557644</v>
+        <v>10.6828901295085</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07607288629882276</v>
+        <v>0.07523692051531922</v>
       </c>
       <c r="W92">
-        <v>0.2178620134107376</v>
+        <v>0.2180591341424878</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3803644314941138</v>
+        <v>0.376184602576596</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.253239989224009</v>
+        <v>0.255139989224009</v>
       </c>
       <c r="C93">
-        <v>-398.3032351750199</v>
+        <v>-406.2608258312215</v>
       </c>
       <c r="D93">
-        <v>151.3407648249801</v>
+        <v>149.9671741687785</v>
       </c>
       <c r="E93">
-        <v>404.744</v>
+        <v>411.328</v>
       </c>
       <c r="F93">
-        <v>599.144</v>
+        <v>605.728</v>
       </c>
       <c r="G93">
         <v>49.5</v>
@@ -8913,37 +8913,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M93">
-        <v>141.2781552</v>
+        <v>142.8306624</v>
       </c>
       <c r="N93">
-        <v>-88.13148853333335</v>
+        <v>-89.68399573333333</v>
       </c>
       <c r="O93">
-        <v>-17.62629770666667</v>
+        <v>-17.93679914666667</v>
       </c>
       <c r="P93">
-        <v>-70.50519082666668</v>
+        <v>-71.74719658666666</v>
       </c>
       <c r="Q93">
-        <v>-66.58519082666668</v>
+        <v>-67.82719658666666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6089575239371685</v>
+        <v>0.6793522144293147</v>
       </c>
       <c r="T93">
-        <v>10.6828901295085</v>
+        <v>12.01825139569706</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07523692051531922</v>
+        <v>0.07441912790102227</v>
       </c>
       <c r="W93">
-        <v>0.2180591341424878</v>
+        <v>0.218251969640939</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.376184602576596</v>
+        <v>0.3720956395051114</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.255139989224009</v>
+        <v>0.257039989224009</v>
       </c>
       <c r="C94">
-        <v>-406.2608258312215</v>
+        <v>-414.1937069401792</v>
       </c>
       <c r="D94">
-        <v>149.9671741687785</v>
+        <v>148.6182930598208</v>
       </c>
       <c r="E94">
-        <v>411.328</v>
+        <v>417.912</v>
       </c>
       <c r="F94">
-        <v>605.728</v>
+        <v>612.312</v>
       </c>
       <c r="G94">
         <v>49.5</v>
@@ -8995,37 +8995,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M94">
-        <v>142.8306624</v>
+        <v>144.3831696</v>
       </c>
       <c r="N94">
-        <v>-89.68399573333333</v>
+        <v>-91.23650293333334</v>
       </c>
       <c r="O94">
-        <v>-17.93679914666667</v>
+        <v>-18.24730058666667</v>
       </c>
       <c r="P94">
-        <v>-71.74719658666666</v>
+        <v>-72.98920234666667</v>
       </c>
       <c r="Q94">
-        <v>-67.82719658666666</v>
+        <v>-69.06920234666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6793522144293147</v>
+        <v>0.7698596736335026</v>
       </c>
       <c r="T94">
-        <v>12.01825139569706</v>
+        <v>13.73514445222521</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07441912790102227</v>
+        <v>0.07361892222466719</v>
       </c>
       <c r="W94">
-        <v>0.218251969640939</v>
+        <v>0.2184406581394235</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3720956395051114</v>
+        <v>0.368094611123336</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.257039989224009</v>
+        <v>0.258939989224009</v>
       </c>
       <c r="C95">
-        <v>-414.1937069401792</v>
+        <v>-422.1025393089981</v>
       </c>
       <c r="D95">
-        <v>148.6182930598208</v>
+        <v>147.293460691002</v>
       </c>
       <c r="E95">
-        <v>417.912</v>
+        <v>424.4960000000001</v>
       </c>
       <c r="F95">
-        <v>612.312</v>
+        <v>618.8960000000001</v>
       </c>
       <c r="G95">
         <v>49.5</v>
@@ -9077,37 +9077,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M95">
-        <v>144.3831696</v>
+        <v>145.9356768</v>
       </c>
       <c r="N95">
-        <v>-91.23650293333334</v>
+        <v>-92.78901013333335</v>
       </c>
       <c r="O95">
-        <v>-18.24730058666667</v>
+        <v>-18.55780202666667</v>
       </c>
       <c r="P95">
-        <v>-72.98920234666667</v>
+        <v>-74.23120810666668</v>
       </c>
       <c r="Q95">
-        <v>-69.06920234666667</v>
+        <v>-70.31120810666668</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7698596736335026</v>
+        <v>0.8905362859057533</v>
       </c>
       <c r="T95">
-        <v>13.73514445222521</v>
+        <v>16.02433519426275</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07361892222466719</v>
+        <v>0.07283574220100052</v>
       </c>
       <c r="W95">
-        <v>0.2184406581394235</v>
+        <v>0.2186253319890041</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.368094611123336</v>
+        <v>0.3641787110050025</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.258939989224009</v>
+        <v>0.260839989224009</v>
       </c>
       <c r="C96">
-        <v>-422.1025393089981</v>
+        <v>-429.9879603903643</v>
       </c>
       <c r="D96">
-        <v>147.293460691002</v>
+        <v>145.9920396096357</v>
       </c>
       <c r="E96">
-        <v>424.4960000000001</v>
+        <v>431.08</v>
       </c>
       <c r="F96">
-        <v>618.8960000000001</v>
+        <v>625.48</v>
       </c>
       <c r="G96">
         <v>49.5</v>
@@ -9159,37 +9159,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M96">
-        <v>145.9356768</v>
+        <v>147.488184</v>
       </c>
       <c r="N96">
-        <v>-92.78901013333335</v>
+        <v>-94.34151733333336</v>
       </c>
       <c r="O96">
-        <v>-18.55780202666667</v>
+        <v>-18.86830346666667</v>
       </c>
       <c r="P96">
-        <v>-74.23120810666668</v>
+        <v>-75.47321386666668</v>
       </c>
       <c r="Q96">
-        <v>-70.31120810666668</v>
+        <v>-71.55321386666668</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8905362859057533</v>
+        <v>1.059483543086905</v>
       </c>
       <c r="T96">
-        <v>16.02433519426275</v>
+        <v>19.22920223311531</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07283574220100052</v>
+        <v>0.07206905017783209</v>
       </c>
       <c r="W96">
-        <v>0.2186253319890041</v>
+        <v>0.2188061179680672</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3641787110050025</v>
+        <v>0.3603452508891604</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.260839989224009</v>
+        <v>0.262739989224009</v>
       </c>
       <c r="C97">
-        <v>-429.9879603903643</v>
+        <v>-437.8505853052567</v>
       </c>
       <c r="D97">
-        <v>145.9920396096357</v>
+        <v>144.7134146947433</v>
       </c>
       <c r="E97">
-        <v>431.08</v>
+        <v>437.6640000000001</v>
       </c>
       <c r="F97">
-        <v>625.48</v>
+        <v>632.0640000000001</v>
       </c>
       <c r="G97">
         <v>49.5</v>
@@ -9241,37 +9241,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M97">
-        <v>147.488184</v>
+        <v>149.0406912</v>
       </c>
       <c r="N97">
-        <v>-94.34151733333336</v>
+        <v>-95.89402453333336</v>
       </c>
       <c r="O97">
-        <v>-18.86830346666667</v>
+        <v>-19.17880490666667</v>
       </c>
       <c r="P97">
-        <v>-75.47321386666668</v>
+        <v>-76.71521962666669</v>
       </c>
       <c r="Q97">
-        <v>-71.55321386666668</v>
+        <v>-72.79521962666669</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.059483543086905</v>
+        <v>1.312904428858631</v>
       </c>
       <c r="T97">
-        <v>19.22920223311531</v>
+        <v>24.03650279139415</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07206905017783209</v>
+        <v>0.07131833090514633</v>
       </c>
       <c r="W97">
-        <v>0.2188061179680672</v>
+        <v>0.2189831375725665</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3603452508891604</v>
+        <v>0.3565916545257316</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.262739989224009</v>
+        <v>0.264639989224009</v>
       </c>
       <c r="C98">
-        <v>-437.8505853052566</v>
+        <v>-445.6910078123815</v>
       </c>
       <c r="D98">
-        <v>144.7134146947433</v>
+        <v>143.4569921876185</v>
       </c>
       <c r="E98">
-        <v>437.664</v>
+        <v>444.2479999999999</v>
       </c>
       <c r="F98">
-        <v>632.064</v>
+        <v>638.6479999999999</v>
       </c>
       <c r="G98">
         <v>49.5</v>
@@ -9323,37 +9323,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M98">
-        <v>149.0406912</v>
+        <v>150.5931984</v>
       </c>
       <c r="N98">
-        <v>-95.89402453333334</v>
+        <v>-97.44653173333332</v>
       </c>
       <c r="O98">
-        <v>-19.17880490666667</v>
+        <v>-19.48930634666667</v>
       </c>
       <c r="P98">
-        <v>-76.71521962666667</v>
+        <v>-77.95722538666665</v>
       </c>
       <c r="Q98">
-        <v>-72.79521962666666</v>
+        <v>-74.03722538666665</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.312904428858628</v>
+        <v>1.735272571811504</v>
       </c>
       <c r="T98">
-        <v>24.03650279139409</v>
+        <v>32.04867038852545</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07131833090514635</v>
+        <v>0.07058309038035103</v>
       </c>
       <c r="W98">
-        <v>0.2189831375725665</v>
+        <v>0.2191565072883132</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3565916545257317</v>
+        <v>0.3529154519017551</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.264639989224009</v>
+        <v>0.266539989224009</v>
       </c>
       <c r="C99">
-        <v>-445.6910078123815</v>
+        <v>-453.5098012275424</v>
       </c>
       <c r="D99">
-        <v>143.4569921876185</v>
+        <v>142.2221987724576</v>
       </c>
       <c r="E99">
-        <v>444.2479999999999</v>
+        <v>450.832</v>
       </c>
       <c r="F99">
-        <v>638.6479999999999</v>
+        <v>645.232</v>
       </c>
       <c r="G99">
         <v>49.5</v>
@@ -9405,37 +9405,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M99">
-        <v>150.5931984</v>
+        <v>152.1457056</v>
       </c>
       <c r="N99">
-        <v>-97.44653173333332</v>
+        <v>-98.99903893333332</v>
       </c>
       <c r="O99">
-        <v>-19.48930634666667</v>
+        <v>-19.79980778666667</v>
       </c>
       <c r="P99">
-        <v>-77.95722538666665</v>
+        <v>-79.19923114666666</v>
       </c>
       <c r="Q99">
-        <v>-74.03722538666665</v>
+        <v>-75.27923114666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.735272571811504</v>
+        <v>2.580008857717255</v>
       </c>
       <c r="T99">
-        <v>32.04867038852545</v>
+        <v>48.07300558278818</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07058309038035103</v>
+        <v>0.06986285476422499</v>
       </c>
       <c r="W99">
-        <v>0.2191565072883132</v>
+        <v>0.2193263388465957</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3529154519017551</v>
+        <v>0.349314273821125</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.266539989224009</v>
+        <v>0.268439989224009</v>
       </c>
       <c r="C100">
-        <v>-453.5098012275424</v>
+        <v>-461.3075192959338</v>
       </c>
       <c r="D100">
-        <v>142.2221987724576</v>
+        <v>141.008480704066</v>
       </c>
       <c r="E100">
-        <v>450.832</v>
+        <v>457.4159999999999</v>
       </c>
       <c r="F100">
-        <v>645.232</v>
+        <v>651.8159999999999</v>
       </c>
       <c r="G100">
         <v>49.5</v>
@@ -9487,37 +9487,37 @@
         <v>53.14666666666666</v>
       </c>
       <c r="M100">
-        <v>152.1457056</v>
+        <v>153.6982128</v>
       </c>
       <c r="N100">
-        <v>-98.99903893333332</v>
+        <v>-100.5515461333333</v>
       </c>
       <c r="O100">
-        <v>-19.79980778666667</v>
+        <v>-20.11030922666667</v>
       </c>
       <c r="P100">
-        <v>-79.19923114666666</v>
+        <v>-80.44123690666666</v>
       </c>
       <c r="Q100">
-        <v>-75.27923114666666</v>
+        <v>-76.52123690666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.580008857717255</v>
+        <v>5.114217715434512</v>
       </c>
       <c r="T100">
-        <v>48.07300558278818</v>
+        <v>96.14601116557637</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06986285476422499</v>
+        <v>0.06915716936256615</v>
       </c>
       <c r="W100">
-        <v>0.2193263388465957</v>
+        <v>0.2194927394643069</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.349314273821125</v>
+        <v>0.3457858468128308</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.268439989224009</v>
-      </c>
-      <c r="C101">
-        <v>-461.3075192959338</v>
-      </c>
-      <c r="D101">
-        <v>141.008480704066</v>
-      </c>
-      <c r="E101">
-        <v>457.4159999999999</v>
-      </c>
-      <c r="F101">
-        <v>651.8159999999999</v>
-      </c>
-      <c r="G101">
-        <v>49.5</v>
-      </c>
-      <c r="H101">
-        <v>464</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>57.06666666666666</v>
-      </c>
-      <c r="K101">
-        <v>3.92</v>
-      </c>
-      <c r="L101">
-        <v>53.14666666666666</v>
-      </c>
-      <c r="M101">
-        <v>153.6982128</v>
-      </c>
-      <c r="N101">
-        <v>-100.5515461333333</v>
-      </c>
-      <c r="O101">
-        <v>-20.11030922666667</v>
-      </c>
-      <c r="P101">
-        <v>-80.44123690666666</v>
-      </c>
-      <c r="Q101">
-        <v>-76.52123690666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.114217715434512</v>
-      </c>
-      <c r="T101">
-        <v>96.14601116557637</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06915716936256615</v>
-      </c>
-      <c r="W101">
-        <v>0.2194927394643069</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3457858468128308</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
